--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -601,7 +601,7 @@
         <v>46153</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>43929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>46153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>44460</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45568</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>45889</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>45730</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44606</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44839</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>44504</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45561</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>46153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>46153</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>44867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>46211</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44587</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46153</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>45189</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>45999</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>46164</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>46174</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>46247</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>46210</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45093</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44628</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>45056</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45352</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45652</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>45042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>45316</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45888</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>46126</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>46126</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>44656</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>46058</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>44748</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>44853</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>44593</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>45110</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45222</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>45188</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45446</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44785</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45604</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45888</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>46141</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>45075</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>46009</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44869</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>45154</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>44917</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>44937</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>45174</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>45104</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44980</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45093</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>45447</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45818</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>45850</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44853</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>45335</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44595</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>44607</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>44860</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>45813</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>44612</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44602</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>45594</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44966</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>45111</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>44917</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44951</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>45279</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>45096</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>45898</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>46141</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>45754</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>45649</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45940</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45758</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>46153</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>46153</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>46153</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>46153</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>45069</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45449</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>46002</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>46002</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>46169</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>44648</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44882</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>44908</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45155</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45215</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>46057</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45545</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>46183</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>46094</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>46190</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45581</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45118</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>46109</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>46126</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45695</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44798</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45730</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>46254</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45307</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45541</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>46230</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>45701</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44909</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>45547</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45616</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44592</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>44830</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45572</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>44603</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>44590</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>46034</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>44491</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44462</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>44630</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44889</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>44474</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>44691</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44859</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>44861</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
         <v>44475</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>44473</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>44581</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44844</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>44816</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44571</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>44645</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>44565</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>44831</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>44783</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>44684</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>44566</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>44806</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>44493</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>44488</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44833</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>44468</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>44587</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44624</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>44776</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>44870</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>44771</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>44657</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>44612</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44617</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>44551</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>44508</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44851</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>44629</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>44594</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44881</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44494</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>44796</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>44551</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>44593</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>44813</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>44785</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>44650</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44839</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>44805</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>44593</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>44526</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44578</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>44634</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>44634</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>44727</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>44551</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>44870</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44587</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>45273</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>45341</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45775</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45022</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>45488</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45123</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>45162</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45230</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>44489</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45092</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>44819</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45054</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>45075</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45091</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>44544</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>44657</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>45606</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>45181</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45278</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>44973</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>44933</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44818</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>44985</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>45561</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45307</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45394</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44692</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45763</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45175</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45103</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45021</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45028</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45649</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45649</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45376</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45327</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45037</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45111</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45728</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44973</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>44494</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44909</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>44909</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45118</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>44594</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>45448</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>45729</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>45107</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>45149</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>45189</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>44833</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45075</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45260</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45106</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45049</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>45222</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>45547</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>45761</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>45121</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>45366</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45260</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45346</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>44992</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>45409</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>44690</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44778</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45664</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>44928</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44867</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>45407</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45338</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45484</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>44959</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>44949</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45063</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45254</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44959</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>45188</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45394</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>44915</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45525</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>44721</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44903</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44890</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45368</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>45369</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>44882</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>44853</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>45331</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45429</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45561</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>45561</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>44497</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45223</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>45210</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>44914</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44914</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>44931</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45091</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45240</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>45096</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>45359</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44832</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>44733</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>45103</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45694</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45754</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>44936</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>45363</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45077</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45849</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>45931</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>46058</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>45191</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>45737</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44865</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>45946</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45217</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>45791</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45849</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45572</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45145</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>45145</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45253</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45163</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>45966</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>45182</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45685</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45975</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44819</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>44609</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>46052</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45713</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>44867</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>44528</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>45603</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>45791</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>45091</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>45698</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>45169</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>45233</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>44505</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>45253</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45103</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45103</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>45603</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>45888</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45628</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>45577</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45478</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29772,7 +29772,7 @@
         <v>45342</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45169</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45166</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>45859</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45321</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>45649</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45914</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45213</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>44868</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45930</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45629</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>45894</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45894</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45135</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>45603</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>44945</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45798</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>44982</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>45211</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>45762</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>45951</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45862</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45966</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45820</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>45841</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45852</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45637</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>44811</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45832</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>45887</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>46141</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45534</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>45908</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45096</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45327</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>45216</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44909</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>44991</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>45840</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>46141</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>45069</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>45679</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32863,7 +32863,7 @@
         <v>44973</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>46141</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>44684</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>44974</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>45057</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>45057</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45392</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45917</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>44972</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>45606</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>45923</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>45217</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>45174</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45385</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45011</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>44645</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>45926</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>45400</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44462</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44463</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45231</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45610</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>45055</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45744</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>45714</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>45664</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>45253</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>45411</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34912,7 +34912,7 @@
         <v>45191</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45938</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45474</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>45649</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>45649</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45938</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45762</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>44917</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>44938</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>45940</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>45943</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>45560</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         <v>44867</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>45945</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>45280</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>44580</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>45946</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>45946</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>45591</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>45043</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>45616</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36460,7 +36460,7 @@
         <v>45426</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>45050</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>45330</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36679,7 +36679,7 @@
         <v>45103</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>44974</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>44693</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>44739</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>46153</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>44494</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45296</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>45958</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>45187</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37346,7 +37346,7 @@
         <v>45958</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>45958</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>44586</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45958</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
         <v>44904</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>46153</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44798</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37862,7 +37862,7 @@
         <v>45733</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45415</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>44977</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45035</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38154,7 +38154,7 @@
         <v>44909</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38227,7 +38227,7 @@
         <v>45090</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38300,7 +38300,7 @@
         <v>44621</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44579</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>45372</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44803</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>44904</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38665,7 +38665,7 @@
         <v>44904</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38738,7 +38738,7 @@
         <v>45560</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45079</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45763</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38957,7 +38957,7 @@
         <v>45197</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>45469</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>45478</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>45975</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>44939</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39322,7 +39322,7 @@
         <v>45980</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>46155</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39473,7 +39473,7 @@
         <v>46155</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39546,7 +39546,7 @@
         <v>45980</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>45980</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39702,7 +39702,7 @@
         <v>45313</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         <v>45079</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45985</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         <v>45090</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39994,7 +39994,7 @@
         <v>45756</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
         <v>45986</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40140,7 +40140,7 @@
         <v>45986</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>45987</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45342</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>44908</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45561</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>46057</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>45894</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45090</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         <v>45110</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>45078</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
         <v>45013</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40953,7 +40953,7 @@
         <v>44900</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>45072</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>44465</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>46160</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>45407</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44970</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45763</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>45477</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41537,7 +41537,7 @@
         <v>45551</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
         <v>44868</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45728</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41761,7 +41761,7 @@
         <v>44866</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>45999</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>45196</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>46000</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45190</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45408</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45369</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>44957</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>44957</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>45695</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45013</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45552</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>45149</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42710,7 +42710,7 @@
         <v>45440</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45082</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44973</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45092</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>45098</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>46168</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>44999</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>44841</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45121</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>45575</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45072</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
         <v>45022</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45470</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>44959</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>46000</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>46029</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>46029</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>44839</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45369</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44107,7 +44107,7 @@
         <v>45093</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>45463</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>45093</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45121</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45561</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>45561</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>44746</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45439</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44701,7 +44701,7 @@
         <v>46034</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45670</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45075</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>45070</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45244</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>44881</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45740</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>44873</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45084</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>44973</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>45442</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>45336</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>44844</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>45079</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>46175</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45315</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45341</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45509</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45510</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>46051</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>46175</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>44713</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>46169</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>45367</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45635</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>46178</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>45475</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45475</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>44825</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46828,7 +46828,7 @@
         <v>45666</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>44497</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46974,7 +46974,7 @@
         <v>46181</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45554</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>46177</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>45071</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>46178</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>45117</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45356</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>46064</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45175</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>44953</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>46064</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45335</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>45335</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>46069</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45218</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>46069</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>46067</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48235,7 +48235,7 @@
         <v>45093</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45078</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>44816</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>44928</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48527,7 +48527,7 @@
         <v>46182</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45414</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>46072</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>46072</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>46072</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>46078</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>44713</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>46184</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45385</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49189,7 +49189,7 @@
         <v>46184</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49262,7 +49262,7 @@
         <v>46083</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>44889</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>46083</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>45111</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>45131</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44756</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49705,7 +49705,7 @@
         <v>45063</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49778,7 +49778,7 @@
         <v>44874</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49851,7 +49851,7 @@
         <v>46086</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45119</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>44677</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45198</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>46087</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>45301</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45301</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>46190</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>46092</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>46092</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>46190</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45512</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>44742</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>45359</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>44713</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45096</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45590</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>46104</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>46106</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>46106</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>44798</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51394,7 +51394,7 @@
         <v>44593</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45098</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>46197</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51618,7 +51618,7 @@
         <v>46197</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45392</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>44746</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51842,7 +51842,7 @@
         <v>46197</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>45056</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51993,7 +51993,7 @@
         <v>46198</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>45118</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>46112</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52212,7 +52212,7 @@
         <v>46112</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52285,7 +52285,7 @@
         <v>46112</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>46112</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>46113</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>45056</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>45544</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>44827</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52723,7 +52723,7 @@
         <v>45016</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52796,7 +52796,7 @@
         <v>44825</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>46122</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52942,7 +52942,7 @@
         <v>46122</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53015,7 +53015,7 @@
         <v>46125</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>46125</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>45095</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>46127</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45244</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53380,7 +53380,7 @@
         <v>46199</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>46127</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>45211</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>46133</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>45367</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53745,7 +53745,7 @@
         <v>46246</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>46246</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>46133</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>45392</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>46134</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45072</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>45244</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54256,7 +54256,7 @@
         <v>46134</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54329,7 +54329,7 @@
         <v>44999</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54402,7 +54402,7 @@
         <v>46134</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54475,7 +54475,7 @@
         <v>45188</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54548,7 +54548,7 @@
         <v>45705</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54621,7 +54621,7 @@
         <v>46134</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54694,7 +54694,7 @@
         <v>46078</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54767,7 +54767,7 @@
         <v>45980</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54845,7 +54845,7 @@
         <v>45478</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         <v>46139</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54991,7 +54991,7 @@
         <v>45644</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45342</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55137,7 +55137,7 @@
         <v>45551</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55210,7 +55210,7 @@
         <v>45931</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55288,7 +55288,7 @@
         <v>44910</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55361,7 +55361,7 @@
         <v>45156</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55434,7 +55434,7 @@
         <v>46246</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>44566</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55580,7 +55580,7 @@
         <v>45373</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55653,7 +55653,7 @@
         <v>45210</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>46250</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>44909</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>44909</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55945,7 +55945,7 @@
         <v>45668</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56018,7 +56018,7 @@
         <v>45156</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56091,7 +56091,7 @@
         <v>44866</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>44755</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56237,7 +56237,7 @@
         <v>44594</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56310,7 +56310,7 @@
         <v>44992</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56383,7 +56383,7 @@
         <v>46248</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45373</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56529,7 +56529,7 @@
         <v>45085</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>45475</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>45205</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56748,7 +56748,7 @@
         <v>46205</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56821,7 +56821,7 @@
         <v>46253</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56899,7 +56899,7 @@
         <v>46253</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56977,7 +56977,7 @@
         <v>44463</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57050,7 +57050,7 @@
         <v>45401</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57123,7 +57123,7 @@
         <v>45239</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57196,7 +57196,7 @@
         <v>45089</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>45079</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57347,7 +57347,7 @@
         <v>46252</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57420,7 +57420,7 @@
         <v>45429</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57493,7 +57493,7 @@
         <v>45762</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57566,7 +57566,7 @@
         <v>44785</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57639,7 +57639,7 @@
         <v>45113</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57712,7 +57712,7 @@
         <v>46255</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57785,7 +57785,7 @@
         <v>44880</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57858,7 +57858,7 @@
         <v>44488</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>46254</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58009,7 +58009,7 @@
         <v>45089</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58082,7 +58082,7 @@
         <v>45208</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58155,7 +58155,7 @@
         <v>45534</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
         <v>45342</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58301,7 +58301,7 @@
         <v>45484</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58374,7 +58374,7 @@
         <v>46255</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58452,7 +58452,7 @@
         <v>45706</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58525,7 +58525,7 @@
         <v>45756</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>44700</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58671,7 +58671,7 @@
         <v>44622</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45240</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58817,7 +58817,7 @@
         <v>44865</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>45744</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58963,7 +58963,7 @@
         <v>45761</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59041,7 +59041,7 @@
         <v>44749</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59114,7 +59114,7 @@
         <v>44973</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59187,7 +59187,7 @@
         <v>45175</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>46261</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59333,7 +59333,7 @@
         <v>45308</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45149</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59479,7 +59479,7 @@
         <v>45210</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59552,7 +59552,7 @@
         <v>44881</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59625,7 +59625,7 @@
         <v>45175</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59698,7 +59698,7 @@
         <v>45371</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59771,7 +59771,7 @@
         <v>44743</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>44594</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59917,7 +59917,7 @@
         <v>45320</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>45741</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45681</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60141,7 +60141,7 @@
         <v>44882</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60214,7 +60214,7 @@
         <v>45679</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60287,7 +60287,7 @@
         <v>45586</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60360,7 +60360,7 @@
         <v>46269</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>46269</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60506,7 +60506,7 @@
         <v>44606</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45545</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60652,7 +60652,7 @@
         <v>45449</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60725,7 +60725,7 @@
         <v>45070</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60798,7 +60798,7 @@
         <v>45601</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60871,7 +60871,7 @@
         <v>45476</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60944,7 +60944,7 @@
         <v>45489</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61017,7 +61017,7 @@
         <v>45587</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61090,7 +61090,7 @@
         <v>46272</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61163,7 +61163,7 @@
         <v>46273</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61236,7 +61236,7 @@
         <v>46274</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61309,7 +61309,7 @@
         <v>45785</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61382,7 +61382,7 @@
         <v>46275</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61460,7 +61460,7 @@
         <v>46279</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61533,7 +61533,7 @@
         <v>46279</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61606,7 +61606,7 @@
         <v>45230</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61679,7 +61679,7 @@
         <v>45489</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61752,7 +61752,7 @@
         <v>45625</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61825,7 +61825,7 @@
         <v>45706</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61898,7 +61898,7 @@
         <v>45786</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61971,7 +61971,7 @@
         <v>45673</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62044,7 +62044,7 @@
         <v>45572</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62117,7 +62117,7 @@
         <v>45665</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62190,7 +62190,7 @@
         <v>45534</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62263,7 +62263,7 @@
         <v>45357</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62336,7 +62336,7 @@
         <v>45301</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62409,7 +62409,7 @@
         <v>45401</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62482,7 +62482,7 @@
         <v>46238</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62560,7 +62560,7 @@
         <v>45367</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62633,7 +62633,7 @@
         <v>45246</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62706,7 +62706,7 @@
         <v>45370</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62779,7 +62779,7 @@
         <v>45792</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62857,7 +62857,7 @@
         <v>45792</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62935,7 +62935,7 @@
         <v>46238</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63013,7 +63013,7 @@
         <v>45701</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63086,7 +63086,7 @@
         <v>45761</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63159,7 +63159,7 @@
         <v>46241</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63232,7 +63232,7 @@
         <v>44697</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63305,7 +63305,7 @@
         <v>46282</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63378,7 +63378,7 @@
         <v>46283</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63451,7 +63451,7 @@
         <v>45525</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63524,7 +63524,7 @@
         <v>45812</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63597,7 +63597,7 @@
         <v>45818</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63670,7 +63670,7 @@
         <v>45821</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63743,7 +63743,7 @@
         <v>45825</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>45824</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63894,7 +63894,7 @@
         <v>45824</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63967,7 +63967,7 @@
         <v>45833</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64040,7 +64040,7 @@
         <v>45834</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64113,7 +64113,7 @@
         <v>45834</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64186,7 +64186,7 @@
         <v>45834</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64259,7 +64259,7 @@
         <v>45834</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64332,7 +64332,7 @@
         <v>45837</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64405,7 +64405,7 @@
         <v>45837</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64478,7 +64478,7 @@
         <v>45616</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64551,7 +64551,7 @@
         <v>45616</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64624,7 +64624,7 @@
         <v>45817</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64697,7 +64697,7 @@
         <v>45846</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64770,7 +64770,7 @@
         <v>45846</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64843,7 +64843,7 @@
         <v>45852</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64916,7 +64916,7 @@
         <v>45856</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64994,7 +64994,7 @@
         <v>45856</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65072,7 +65072,7 @@
         <v>45818</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65145,7 +65145,7 @@
         <v>45616</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65218,7 +65218,7 @@
         <v>45881</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65296,7 +65296,7 @@
         <v>45880</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65369,7 +65369,7 @@
         <v>45880</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65442,7 +65442,7 @@
         <v>45882</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65515,7 +65515,7 @@
         <v>45882</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65588,7 +65588,7 @@
         <v>45883</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65661,7 +65661,7 @@
         <v>45883</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65734,7 +65734,7 @@
         <v>44665</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65807,7 +65807,7 @@
         <v>44973</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65880,7 +65880,7 @@
         <v>45422</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65953,7 +65953,7 @@
         <v>45649</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66026,7 +66026,7 @@
         <v>45457</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66099,7 +66099,7 @@
         <v>45088</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66172,7 +66172,7 @@
         <v>45469</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66245,7 +66245,7 @@
         <v>45000</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66318,7 +66318,7 @@
         <v>45224</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66391,7 +66391,7 @@
         <v>45572</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66464,7 +66464,7 @@
         <v>45056</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66537,7 +66537,7 @@
         <v>44592</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66610,7 +66610,7 @@
         <v>45558</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66683,7 +66683,7 @@
         <v>44587</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66756,7 +66756,7 @@
         <v>44806</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66829,7 +66829,7 @@
         <v>45649</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66902,7 +66902,7 @@
         <v>45056</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66975,7 +66975,7 @@
         <v>45649</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67048,7 +67048,7 @@
         <v>44594</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67121,7 +67121,7 @@
         <v>44693</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67194,7 +67194,7 @@
         <v>45357</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67267,7 +67267,7 @@
         <v>45088</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67340,7 +67340,7 @@
         <v>45335</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67413,7 +67413,7 @@
         <v>45231</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67486,7 +67486,7 @@
         <v>44587</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67559,7 +67559,7 @@
         <v>45572</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67632,7 +67632,7 @@
         <v>45056</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67705,7 +67705,7 @@
         <v>45750</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67778,7 +67778,7 @@
         <v>45847</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67851,7 +67851,7 @@
         <v>45923</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67924,7 +67924,7 @@
         <v>45919</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67997,7 +67997,7 @@
         <v>45926</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68070,7 +68070,7 @@
         <v>45982</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68143,7 +68143,7 @@
         <v>45982</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68216,7 +68216,7 @@
         <v>46030</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68289,7 +68289,7 @@
         <v>46244</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -601,7 +601,7 @@
         <v>46153</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>43929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>46153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45568</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45889</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45730</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45358</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44606</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>44839</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>46153</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44504</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>45561</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>44867</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>46153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>46153</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>46211</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>45643</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45999</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>46153</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>46164</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>46210</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>45189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46247</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44628</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>45056</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45316</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>45352</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>45042</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45652</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44656</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>45888</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45695</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>46126</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>46126</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>46058</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>44748</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44853</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>44593</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>45174</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>45888</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>45075</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>45110</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44785</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45818</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45093</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>46009</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>46141</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>44869</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45188</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44937</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45446</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45850</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>45447</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>45104</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45604</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44917</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45222</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44980</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44595</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>44607</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44853</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>45335</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44860</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45813</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44612</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>45215</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>45096</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45898</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45545</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>44908</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>46057</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>45758</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>45449</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>45940</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45581</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>46094</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>46109</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>46126</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>46002</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>46002</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>46141</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>46153</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>46153</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>46153</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>45616</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>46169</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>45155</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>45594</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>46183</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45118</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>46190</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44648</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>46254</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45307</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>45730</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>46230</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44917</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>46153</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44798</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>45069</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45111</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44966</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>44951</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45649</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44882</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>45279</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45541</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44909</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45547</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45701</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44592</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>44603</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44590</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>44830</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45572</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>44491</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44630</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44889</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>44474</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44691</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44859</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44861</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44475</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44473</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>44581</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44816</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>44571</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>44844</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44645</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44565</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44831</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>44783</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>44566</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>44684</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>44806</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44493</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>44488</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>44833</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>44468</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>44587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>44624</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44776</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>44870</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>44771</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>44657</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>44612</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44617</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>44551</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>44508</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>44851</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44494</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>44629</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>44881</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>44796</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44551</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>44593</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>44813</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>44785</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44650</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44839</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>44805</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44593</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>44526</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>44578</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44634</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44634</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>44727</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44870</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>44551</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>44587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>45043</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45091</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>45054</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45216</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45341</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45510</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>44866</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>44866</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>44755</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>44867</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45075</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45253</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>45190</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45342</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>44827</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45336</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44890</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45093</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45103</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45103</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45376</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45440</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45149</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45469</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>44868</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>45478</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45359</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>44839</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45078</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45685</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44973</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>44973</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45701</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45791</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44505</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45233</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>44957</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44957</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45883</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45883</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>46000</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45698</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45603</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>45761</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45342</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45603</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>44528</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>45603</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44982</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>46029</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>46029</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>45849</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>45882</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>45169</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>44936</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>46034</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>44609</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45888</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>45628</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45341</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45166</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>45475</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>45475</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45729</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45894</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45894</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>44915</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44972</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45089</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45551</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44488</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45798</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44697</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45852</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44914</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45547</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45544</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45908</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>46051</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45840</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>44904</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45442</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>44959</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45664</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45917</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44928</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>44544</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>46064</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44959</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>46064</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>45525</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>46069</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>46067</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>46069</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>44692</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45923</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45561</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45561</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45103</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>46072</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45408</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>46072</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>46072</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>44992</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>45926</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45098</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>44873</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>46078</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>45145</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45145</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44593</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>46083</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>46083</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>45335</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>45222</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>44973</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>45385</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>46087</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44910</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>46086</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45372</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45037</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>44939</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>45223</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>45230</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>45367</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>46092</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>46092</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>45938</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>45940</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>44733</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>44867</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>45943</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44970</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>45191</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>45945</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>45812</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>45946</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>45946</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45095</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>45695</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>46104</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>44713</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>46106</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45415</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45071</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45586</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45439</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>46106</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45740</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>44825</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>45070</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45367</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45411</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45958</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45958</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>46113</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45958</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>45958</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>46112</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>46112</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>46112</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>46112</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>44713</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45121</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45121</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44746</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44798</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>45307</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45359</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>45089</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>46122</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45629</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44931</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>46122</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>46125</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46125</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45106</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>46127</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>45057</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45057</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>46127</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>44819</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45975</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45681</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>45980</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45980</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45980</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>46133</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>46134</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45754</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45210</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>46134</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>46134</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45475</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>46133</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>45986</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>44999</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45985</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45478</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45966</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45363</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45914</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45930</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45820</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>45986</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45841</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45966</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45705</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45951</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45478</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45577</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45980</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45987</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>45931</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>45392</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45859</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45975</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45706</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45644</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>45551</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45119</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>45931</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45862</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45713</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45484</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>45409</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>45694</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45887</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>45327</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35153,7 +35153,7 @@
         <v>45999</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35226,7 +35226,7 @@
         <v>46000</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>46052</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>45022</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45111</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>45077</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45946</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45231</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>45818</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>45098</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35883,7 +35883,7 @@
         <v>45534</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35956,7 +35956,7 @@
         <v>45572</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>44818</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36102,7 +36102,7 @@
         <v>45369</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45762</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45824</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>44945</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>44494</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>46139</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45733</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>45832</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>45821</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45824</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44991</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>46078</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45554</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>44816</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>44881</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>44844</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>46058</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45825</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45509</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>45189</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>45728</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>46141</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>44700</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45072</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>46141</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>44889</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>45392</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>45135</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45055</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>45111</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>46141</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>45761</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>45426</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45763</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>46153</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45834</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>44874</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>45834</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>45013</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45090</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45834</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>46153</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>45833</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45834</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>44882</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>45210</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>46155</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39588,7 +39588,7 @@
         <v>45296</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39661,7 +39661,7 @@
         <v>45894</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>46160</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39807,7 +39807,7 @@
         <v>44825</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>45342</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45096</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40026,7 +40026,7 @@
         <v>45103</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>46057</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>45575</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45837</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45837</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>45156</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45313</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>45561</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>45761</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>45394</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45368</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>45369</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>45616</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45846</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45817</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45846</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45118</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45121</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>45280</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45616</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45123</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45117</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41642,7 +41642,7 @@
         <v>46168</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45852</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41788,7 +41788,7 @@
         <v>45084</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45561</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>44489</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>45856</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>45856</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45079</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>45107</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44465</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>44953</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45670</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>45156</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>45818</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>46175</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45616</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45429</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>46169</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>44938</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>46177</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>44973</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45744</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45260</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>46181</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>46178</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>46178</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45616</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>46184</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43711,7 +43711,7 @@
         <v>45096</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>46184</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>45474</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45169</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>44580</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>46182</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45079</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>45320</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44300,7 +44300,7 @@
         <v>45113</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>46190</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44446,7 +44446,7 @@
         <v>45131</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44519,7 +44519,7 @@
         <v>45763</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44592,7 +44592,7 @@
         <v>46190</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45315</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44738,7 +44738,7 @@
         <v>45016</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44811,7 +44811,7 @@
         <v>45561</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>44566</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45092</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45197</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>46197</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>45880</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>46197</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>46197</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45035</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44832</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45218</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45880</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45338</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45560</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>44645</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>46199</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>46198</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45881</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45882</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45664</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45791</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45737</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>46205</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>44677</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45253</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45373</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45849</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45253</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>45063</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>45082</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>45191</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>44657</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>44594</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>46250</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45049</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>44622</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>46252</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45637</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>46254</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45072</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45762</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>46253</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>46253</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45118</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>45392</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45196</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>44833</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>44690</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>44684</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>46255</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45182</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>45175</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>45093</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>46255</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45244</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48901,7 +48901,7 @@
         <v>45741</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>45756</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>45211</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49120,7 +49120,7 @@
         <v>45187</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49193,7 +49193,7 @@
         <v>46261</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49266,7 +49266,7 @@
         <v>45407</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         <v>45239</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44742</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>44909</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45175</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45198</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>45211</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>44749</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>44721</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>44743</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>45175</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45414</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45756</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>44909</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50288,7 +50288,7 @@
         <v>45244</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50361,7 +50361,7 @@
         <v>44841</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45775</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>44803</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>44693</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>45448</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>44739</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50804,7 +50804,7 @@
         <v>44746</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45254</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>45330</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>44497</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>44974</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>46269</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>46272</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>46269</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>45366</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>45217</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>44917</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51612,7 +51612,7 @@
         <v>46273</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>44959</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51758,7 +51758,7 @@
         <v>46274</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51831,7 +51831,7 @@
         <v>45273</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>44819</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51982,7 +51982,7 @@
         <v>45301</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45301</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52128,7 +52128,7 @@
         <v>45763</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52201,7 +52201,7 @@
         <v>45327</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52274,7 +52274,7 @@
         <v>45092</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45346</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52425,7 +52425,7 @@
         <v>45728</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>46275</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52581,7 +52581,7 @@
         <v>46279</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52654,7 +52654,7 @@
         <v>45278</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52727,7 +52727,7 @@
         <v>45090</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52800,7 +52800,7 @@
         <v>45610</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>44756</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52951,7 +52951,7 @@
         <v>45091</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>44868</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53097,7 +53097,7 @@
         <v>44621</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53170,7 +53170,7 @@
         <v>46279</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53243,7 +53243,7 @@
         <v>46282</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         <v>45484</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>46238</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53467,7 +53467,7 @@
         <v>44865</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53540,7 +53540,7 @@
         <v>44985</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53613,7 +53613,7 @@
         <v>46238</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>45463</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53764,7 +53764,7 @@
         <v>45534</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>46283</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53910,7 +53910,7 @@
         <v>45394</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53988,7 +53988,7 @@
         <v>45090</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>45342</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54134,7 +54134,7 @@
         <v>46175</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54207,7 +54207,7 @@
         <v>45400</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>46241</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>45552</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>44909</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         <v>44973</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>45744</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>46286</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>44904</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>45174</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54864,7 +54864,7 @@
         <v>45335</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54942,7 +54942,7 @@
         <v>44992</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55015,7 +55015,7 @@
         <v>44579</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>44928</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55161,7 +55161,7 @@
         <v>44594</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>44933</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>44977</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55380,7 +55380,7 @@
         <v>44881</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45188</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55526,7 +55526,7 @@
         <v>45244</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55599,7 +55599,7 @@
         <v>46248</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55672,7 +55672,7 @@
         <v>45072</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55745,7 +55745,7 @@
         <v>45371</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>44914</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>46134</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55964,7 +55964,7 @@
         <v>44497</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56037,7 +56037,7 @@
         <v>44949</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56110,7 +56110,7 @@
         <v>45512</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45260</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56256,7 +56256,7 @@
         <v>46246</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56329,7 +56329,7 @@
         <v>46246</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>45188</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56475,7 +56475,7 @@
         <v>46246</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56548,7 +56548,7 @@
         <v>44909</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56621,7 +56621,7 @@
         <v>45792</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45385</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56772,7 +56772,7 @@
         <v>45056</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45606</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45938</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56991,7 +56991,7 @@
         <v>45075</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>46289</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>44594</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>44900</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>45213</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>44904</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>44909</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57502,7 +57502,7 @@
         <v>45091</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57575,7 +57575,7 @@
         <v>44494</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57648,7 +57648,7 @@
         <v>45063</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57721,7 +57721,7 @@
         <v>44798</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>44853</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45470</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57940,7 +57940,7 @@
         <v>45021</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58013,7 +58013,7 @@
         <v>45079</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58086,7 +58086,7 @@
         <v>45668</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>44713</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58232,7 +58232,7 @@
         <v>44908</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58305,7 +58305,7 @@
         <v>44974</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58378,7 +58378,7 @@
         <v>45079</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58451,7 +58451,7 @@
         <v>45208</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58524,7 +58524,7 @@
         <v>45525</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58597,7 +58597,7 @@
         <v>45590</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58670,7 +58670,7 @@
         <v>45175</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58743,7 +58743,7 @@
         <v>44973</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>45078</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58889,7 +58889,7 @@
         <v>45488</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58962,7 +58962,7 @@
         <v>45050</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59035,7 +59035,7 @@
         <v>45401</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59108,7 +59108,7 @@
         <v>45149</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59181,7 +59181,7 @@
         <v>45075</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45679</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>44880</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>45606</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>44586</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59546,7 +59546,7 @@
         <v>45093</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59619,7 +59619,7 @@
         <v>45162</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59692,7 +59692,7 @@
         <v>44865</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59765,7 +59765,7 @@
         <v>44909</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59838,7 +59838,7 @@
         <v>45085</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59911,7 +59911,7 @@
         <v>45308</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>45649</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60057,7 +60057,7 @@
         <v>45649</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45240</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60203,7 +60203,7 @@
         <v>44785</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60276,7 +60276,7 @@
         <v>45011</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60349,7 +60349,7 @@
         <v>45210</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60422,7 +60422,7 @@
         <v>45110</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60500,7 +60500,7 @@
         <v>45591</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60573,7 +60573,7 @@
         <v>45635</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60646,7 +60646,7 @@
         <v>45028</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60719,7 +60719,7 @@
         <v>44811</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60792,7 +60792,7 @@
         <v>44867</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         <v>45429</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60938,7 +60938,7 @@
         <v>44594</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61011,7 +61011,7 @@
         <v>45331</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61084,7 +61084,7 @@
         <v>45022</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61157,7 +61157,7 @@
         <v>44778</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45056</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61303,7 +61303,7 @@
         <v>45149</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61376,7 +61376,7 @@
         <v>45561</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61454,7 +61454,7 @@
         <v>45205</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61527,7 +61527,7 @@
         <v>45103</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61600,7 +61600,7 @@
         <v>45240</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61673,7 +61673,7 @@
         <v>44903</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61746,7 +61746,7 @@
         <v>45477</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61819,7 +61819,7 @@
         <v>45407</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61892,7 +61892,7 @@
         <v>44882</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61965,7 +61965,7 @@
         <v>45069</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62038,7 +62038,7 @@
         <v>45163</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45373</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62184,7 +62184,7 @@
         <v>45369</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62257,7 +62257,7 @@
         <v>45356</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62330,7 +62330,7 @@
         <v>45321</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62403,7 +62403,7 @@
         <v>45013</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62476,7 +62476,7 @@
         <v>45560</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62549,7 +62549,7 @@
         <v>45096</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62622,7 +62622,7 @@
         <v>45679</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62695,7 +62695,7 @@
         <v>45714</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62768,7 +62768,7 @@
         <v>45649</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62841,7 +62841,7 @@
         <v>45649</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62914,7 +62914,7 @@
         <v>45649</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>45217</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63060,7 +63060,7 @@
         <v>45762</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63133,7 +63133,7 @@
         <v>44999</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63206,7 +63206,7 @@
         <v>45666</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63279,7 +63279,7 @@
         <v>45181</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63352,7 +63352,7 @@
         <v>45070</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63425,7 +63425,7 @@
         <v>44606</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63498,7 +63498,7 @@
         <v>45601</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63571,7 +63571,7 @@
         <v>45449</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63644,7 +63644,7 @@
         <v>45545</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63717,7 +63717,7 @@
         <v>45476</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63790,7 +63790,7 @@
         <v>45489</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>45587</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63936,7 +63936,7 @@
         <v>45665</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>45706</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>45572</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64155,7 +64155,7 @@
         <v>45230</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64228,7 +64228,7 @@
         <v>45370</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64301,7 +64301,7 @@
         <v>45246</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64374,7 +64374,7 @@
         <v>45357</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64447,7 +64447,7 @@
         <v>45367</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64520,7 +64520,7 @@
         <v>45673</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64593,7 +64593,7 @@
         <v>45301</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64666,7 +64666,7 @@
         <v>45625</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
         <v>45489</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64812,7 +64812,7 @@
         <v>45785</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>45786</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64958,7 +64958,7 @@
         <v>45401</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65031,7 +65031,7 @@
         <v>45534</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65104,7 +65104,7 @@
         <v>44665</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65177,7 +65177,7 @@
         <v>44592</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65250,7 +65250,7 @@
         <v>44587</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65323,7 +65323,7 @@
         <v>44594</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65396,7 +65396,7 @@
         <v>44693</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65469,7 +65469,7 @@
         <v>44587</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65542,7 +65542,7 @@
         <v>44973</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65615,7 +65615,7 @@
         <v>45422</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65688,7 +65688,7 @@
         <v>45649</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65761,7 +65761,7 @@
         <v>45457</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65834,7 +65834,7 @@
         <v>45088</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65907,7 +65907,7 @@
         <v>45469</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65980,7 +65980,7 @@
         <v>45000</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66053,7 +66053,7 @@
         <v>45224</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66126,7 +66126,7 @@
         <v>45572</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66199,7 +66199,7 @@
         <v>45056</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66272,7 +66272,7 @@
         <v>45558</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66345,7 +66345,7 @@
         <v>44806</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66418,7 +66418,7 @@
         <v>45649</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66491,7 +66491,7 @@
         <v>45056</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66564,7 +66564,7 @@
         <v>45649</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66637,7 +66637,7 @@
         <v>45357</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66710,7 +66710,7 @@
         <v>45088</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66783,7 +66783,7 @@
         <v>45335</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66856,7 +66856,7 @@
         <v>45231</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66929,7 +66929,7 @@
         <v>45572</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67002,7 +67002,7 @@
         <v>45056</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67075,7 +67075,7 @@
         <v>45750</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67148,7 +67148,7 @@
         <v>45847</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67221,7 +67221,7 @@
         <v>45923</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67294,7 +67294,7 @@
         <v>45919</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67367,7 +67367,7 @@
         <v>45926</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67440,7 +67440,7 @@
         <v>45982</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67513,7 +67513,7 @@
         <v>45982</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67586,7 +67586,7 @@
         <v>46030</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67659,7 +67659,7 @@
         <v>46244</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -601,7 +601,7 @@
         <v>46153</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>43929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>46153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45568</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45889</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45730</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45358</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44606</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>44839</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>46153</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44504</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>45561</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>44867</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>46153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>46153</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>46211</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>45643</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45999</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>46153</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>46164</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>46210</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>45189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46247</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44628</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>45056</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45316</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>45352</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>45042</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45652</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44656</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>45888</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45695</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>46126</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>46126</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>46058</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>44748</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44853</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>44593</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>45174</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>45888</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>45075</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>45110</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44785</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45818</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45093</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>46009</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>46141</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>44869</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45188</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44937</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45446</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45850</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>45447</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>45104</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45604</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44917</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45222</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44980</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44595</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>44607</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44853</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>45335</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44860</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45813</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44612</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>45215</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>45096</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45898</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45545</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>44908</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>46057</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>45758</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>45449</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>45940</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45581</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>46094</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>46109</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>46126</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>46002</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>46002</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>46141</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>46153</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>46153</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>46153</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>45616</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>46169</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>45155</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>45594</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>46183</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45118</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>46190</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44648</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>46254</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45307</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>45730</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>46230</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44917</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>46153</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44798</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>45069</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45111</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44966</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>44951</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45649</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44882</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>45279</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45541</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44909</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45547</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45701</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44592</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>44603</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44590</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>44830</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45572</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>44491</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44630</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44889</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>44474</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44691</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44859</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44861</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44475</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44473</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>44581</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44816</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>44571</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>44844</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44645</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44565</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44831</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>44783</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>44566</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>44684</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>44806</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44493</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>44488</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>44833</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>44468</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>44587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>44624</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44776</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>44870</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>44771</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>44657</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>44612</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44617</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>44551</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>44508</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>44851</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44494</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>44629</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>44881</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>44796</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>44551</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>44593</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>44813</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>44785</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44650</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44839</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>44805</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44593</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>44526</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>44578</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44634</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44634</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>44727</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44870</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>44551</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>44587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>45043</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45091</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>45054</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45216</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45341</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45510</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>44866</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>44866</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>44755</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>44867</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45075</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45253</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>45190</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45342</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>44827</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45336</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44890</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45093</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45103</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45103</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45376</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45440</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45149</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45469</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>44868</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>45478</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45359</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>44839</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45078</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45685</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44973</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>44973</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45701</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45791</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44505</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45233</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>44957</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44957</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45883</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45883</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>46000</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45698</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45603</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>45761</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45342</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45603</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>44528</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>45603</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44982</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>46029</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>46029</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>45849</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>45882</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>45169</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>44936</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>46034</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>44609</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45888</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>45628</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45341</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45166</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>45475</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>45475</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45729</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45894</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45894</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>44915</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44972</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45089</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45551</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44488</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45798</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44697</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45852</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44914</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45547</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45544</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45908</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>46051</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45840</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>44904</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45442</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>44959</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45664</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45917</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44928</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>44544</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>46064</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44959</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>46064</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>45525</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>46069</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>46067</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>46069</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>44692</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45923</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45561</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45561</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45103</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>46072</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45408</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>46072</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>46072</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>44992</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>45926</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45098</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>44873</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>46078</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>45145</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45145</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44593</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>46083</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>46083</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>45335</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>45222</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>44973</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>45385</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>46087</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44910</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>46086</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45372</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45037</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>44939</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>45223</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>45230</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>45367</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>46092</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>46092</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>45938</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>45940</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>44733</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>44867</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>45943</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44970</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>45191</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>45945</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>45812</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>45946</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>45946</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45095</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>45695</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>46104</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>44713</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>46106</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45415</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45071</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45586</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45439</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>46106</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45740</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>44825</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>45070</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45367</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45411</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45958</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45958</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>46113</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45958</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>45958</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>46112</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>46112</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>46112</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>46112</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>44713</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45121</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45121</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44746</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44798</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>45307</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45359</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>45089</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>46122</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45629</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44931</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>46122</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>46125</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46125</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45106</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>46127</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>45057</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45057</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>46127</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>44819</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45975</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45681</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>45980</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45980</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45980</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>46133</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>46134</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45754</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45210</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>46134</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>46134</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45475</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>46133</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>45986</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>44999</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45985</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45478</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45966</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45363</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45914</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45930</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45820</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>45986</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45841</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45966</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45705</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45951</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45478</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45577</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45980</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45987</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>45931</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>45392</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45859</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45975</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45706</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45644</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>45551</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45119</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>45931</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45862</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45713</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45484</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>45409</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>45694</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45887</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>45327</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35153,7 +35153,7 @@
         <v>45999</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35226,7 +35226,7 @@
         <v>46000</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>46052</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>45022</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45111</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>45077</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45946</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45231</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>45818</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>45098</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35883,7 +35883,7 @@
         <v>45534</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35956,7 +35956,7 @@
         <v>45572</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>44818</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36102,7 +36102,7 @@
         <v>45369</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45762</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45824</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>44945</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>44494</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>46139</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45733</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>45832</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>45821</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45824</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>44991</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>46078</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45554</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>44816</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>44881</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>44844</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>46058</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45825</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45509</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>45189</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>45728</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>46141</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>44700</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45072</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>46141</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>44889</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>45392</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>45135</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45055</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>45111</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>46141</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>45761</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>45426</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45763</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>46153</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45834</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>44874</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>45834</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>45013</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45090</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45834</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>46153</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>45833</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45834</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>44882</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>45210</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>46155</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39588,7 +39588,7 @@
         <v>45296</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39661,7 +39661,7 @@
         <v>45894</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>46160</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39807,7 +39807,7 @@
         <v>44825</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>45342</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45096</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40026,7 +40026,7 @@
         <v>45103</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>46057</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>45575</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45837</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45837</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>45156</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45313</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>45561</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>45761</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>45394</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45368</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>45369</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>45616</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45846</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45817</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45846</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45118</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45121</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>45280</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45616</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45123</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45117</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41642,7 +41642,7 @@
         <v>46168</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45852</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41788,7 +41788,7 @@
         <v>45084</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45561</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>44489</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>45856</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>45856</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45079</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>45107</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44465</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>44953</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45670</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>45156</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>45818</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>46175</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45616</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45429</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>46169</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>44938</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>46177</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>44973</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45744</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45260</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>46181</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>46178</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>46178</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45616</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>46184</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43711,7 +43711,7 @@
         <v>45096</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>46184</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>45474</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45169</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>44580</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>46182</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45079</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>45320</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44300,7 +44300,7 @@
         <v>45113</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>46190</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44446,7 +44446,7 @@
         <v>45131</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44519,7 +44519,7 @@
         <v>45763</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44592,7 +44592,7 @@
         <v>46190</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45315</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44738,7 +44738,7 @@
         <v>45016</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44811,7 +44811,7 @@
         <v>45561</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>44566</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45092</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45197</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>46197</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>45880</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>46197</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>46197</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45035</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44832</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45218</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45880</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45338</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45560</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>44645</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>46199</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>46198</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45881</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45882</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45664</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45791</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45737</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>46205</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>44677</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45253</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45373</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45849</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45253</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>45063</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>45082</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>45191</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>44657</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>44594</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>46250</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45049</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>44622</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>46252</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45637</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>46254</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45072</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45762</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>46253</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>46253</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45118</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>45392</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45196</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>44833</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>44690</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>44684</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>46255</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45182</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>45175</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>45093</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>46255</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45244</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48901,7 +48901,7 @@
         <v>45741</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>45756</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>45211</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49120,7 +49120,7 @@
         <v>45187</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49193,7 +49193,7 @@
         <v>46261</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49266,7 +49266,7 @@
         <v>45407</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         <v>45239</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44742</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>44909</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45175</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45198</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>45211</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>44749</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>44721</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>44743</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>45175</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45414</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45756</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>44909</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50288,7 +50288,7 @@
         <v>45244</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50361,7 +50361,7 @@
         <v>44841</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45775</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>44803</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>44693</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>45448</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>44739</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50804,7 +50804,7 @@
         <v>44746</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45254</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>45330</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>44497</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>44974</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>46269</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>46272</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>46269</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>45366</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>45217</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>44917</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51612,7 +51612,7 @@
         <v>46273</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>44959</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51758,7 +51758,7 @@
         <v>46274</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51831,7 +51831,7 @@
         <v>45273</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>44819</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51982,7 +51982,7 @@
         <v>45301</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45301</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52128,7 +52128,7 @@
         <v>45763</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52201,7 +52201,7 @@
         <v>45327</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52274,7 +52274,7 @@
         <v>45092</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45346</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52425,7 +52425,7 @@
         <v>45728</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>46275</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52581,7 +52581,7 @@
         <v>46279</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52654,7 +52654,7 @@
         <v>45278</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52727,7 +52727,7 @@
         <v>45090</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52800,7 +52800,7 @@
         <v>45610</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>44756</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52951,7 +52951,7 @@
         <v>45091</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>44868</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53097,7 +53097,7 @@
         <v>44621</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53170,7 +53170,7 @@
         <v>46279</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53243,7 +53243,7 @@
         <v>46282</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         <v>45484</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>46238</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53467,7 +53467,7 @@
         <v>44865</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53540,7 +53540,7 @@
         <v>44985</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53613,7 +53613,7 @@
         <v>46238</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>45463</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53764,7 +53764,7 @@
         <v>45534</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>46283</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53910,7 +53910,7 @@
         <v>45394</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53988,7 +53988,7 @@
         <v>45090</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>45342</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54134,7 +54134,7 @@
         <v>46175</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54207,7 +54207,7 @@
         <v>45400</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>46241</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>45552</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>44909</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         <v>44973</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>45744</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>46286</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>44904</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>45174</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54864,7 +54864,7 @@
         <v>45335</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54942,7 +54942,7 @@
         <v>44992</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55015,7 +55015,7 @@
         <v>44579</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>44928</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55161,7 +55161,7 @@
         <v>44594</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>44933</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>44977</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55380,7 +55380,7 @@
         <v>44881</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45188</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55526,7 +55526,7 @@
         <v>45244</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55599,7 +55599,7 @@
         <v>46248</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55672,7 +55672,7 @@
         <v>45072</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55745,7 +55745,7 @@
         <v>45371</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>44914</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>46134</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55964,7 +55964,7 @@
         <v>44497</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56037,7 +56037,7 @@
         <v>44949</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56110,7 +56110,7 @@
         <v>45512</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45260</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56256,7 +56256,7 @@
         <v>46246</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56329,7 +56329,7 @@
         <v>46246</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>45188</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56475,7 +56475,7 @@
         <v>46246</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56548,7 +56548,7 @@
         <v>44909</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56621,7 +56621,7 @@
         <v>45792</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45385</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56772,7 +56772,7 @@
         <v>45056</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45606</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45938</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56991,7 +56991,7 @@
         <v>45075</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>46289</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>44594</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>44900</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>45213</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>44904</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>44909</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57502,7 +57502,7 @@
         <v>45091</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57575,7 +57575,7 @@
         <v>44494</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57648,7 +57648,7 @@
         <v>45063</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57721,7 +57721,7 @@
         <v>44798</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>44853</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45470</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57940,7 +57940,7 @@
         <v>45021</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58013,7 +58013,7 @@
         <v>45079</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58086,7 +58086,7 @@
         <v>45668</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>44713</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58232,7 +58232,7 @@
         <v>44908</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58305,7 +58305,7 @@
         <v>44974</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58378,7 +58378,7 @@
         <v>45079</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58451,7 +58451,7 @@
         <v>45208</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58524,7 +58524,7 @@
         <v>45525</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58597,7 +58597,7 @@
         <v>45590</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58670,7 +58670,7 @@
         <v>45175</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58743,7 +58743,7 @@
         <v>44973</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>45078</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58889,7 +58889,7 @@
         <v>45488</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58962,7 +58962,7 @@
         <v>45050</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59035,7 +59035,7 @@
         <v>45401</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59108,7 +59108,7 @@
         <v>45149</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59181,7 +59181,7 @@
         <v>45075</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45679</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>44880</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>45606</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>44586</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59546,7 +59546,7 @@
         <v>45093</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59619,7 +59619,7 @@
         <v>45162</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59692,7 +59692,7 @@
         <v>44865</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59765,7 +59765,7 @@
         <v>44909</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59838,7 +59838,7 @@
         <v>45085</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59911,7 +59911,7 @@
         <v>45308</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>45649</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60057,7 +60057,7 @@
         <v>45649</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45240</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60203,7 +60203,7 @@
         <v>44785</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60276,7 +60276,7 @@
         <v>45011</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60349,7 +60349,7 @@
         <v>45210</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60422,7 +60422,7 @@
         <v>45110</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60500,7 +60500,7 @@
         <v>45591</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60573,7 +60573,7 @@
         <v>45635</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60646,7 +60646,7 @@
         <v>45028</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60719,7 +60719,7 @@
         <v>44811</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60792,7 +60792,7 @@
         <v>44867</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         <v>45429</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60938,7 +60938,7 @@
         <v>44594</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61011,7 +61011,7 @@
         <v>45331</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61084,7 +61084,7 @@
         <v>45022</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61157,7 +61157,7 @@
         <v>44778</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45056</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61303,7 +61303,7 @@
         <v>45149</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61376,7 +61376,7 @@
         <v>45561</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61454,7 +61454,7 @@
         <v>45205</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61527,7 +61527,7 @@
         <v>45103</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61600,7 +61600,7 @@
         <v>45240</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61673,7 +61673,7 @@
         <v>44903</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61746,7 +61746,7 @@
         <v>45477</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61819,7 +61819,7 @@
         <v>45407</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61892,7 +61892,7 @@
         <v>44882</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61965,7 +61965,7 @@
         <v>45069</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62038,7 +62038,7 @@
         <v>45163</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45373</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62184,7 +62184,7 @@
         <v>45369</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62257,7 +62257,7 @@
         <v>45356</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62330,7 +62330,7 @@
         <v>45321</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62403,7 +62403,7 @@
         <v>45013</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62476,7 +62476,7 @@
         <v>45560</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62549,7 +62549,7 @@
         <v>45096</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62622,7 +62622,7 @@
         <v>45679</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62695,7 +62695,7 @@
         <v>45714</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62768,7 +62768,7 @@
         <v>45649</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62841,7 +62841,7 @@
         <v>45649</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62914,7 +62914,7 @@
         <v>45649</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>45217</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63060,7 +63060,7 @@
         <v>45762</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63133,7 +63133,7 @@
         <v>44999</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63206,7 +63206,7 @@
         <v>45666</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63279,7 +63279,7 @@
         <v>45181</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63352,7 +63352,7 @@
         <v>45070</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63425,7 +63425,7 @@
         <v>44606</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63498,7 +63498,7 @@
         <v>45601</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63571,7 +63571,7 @@
         <v>45449</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63644,7 +63644,7 @@
         <v>45545</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63717,7 +63717,7 @@
         <v>45476</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63790,7 +63790,7 @@
         <v>45489</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>45587</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63936,7 +63936,7 @@
         <v>45665</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>45706</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>45572</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64155,7 +64155,7 @@
         <v>45230</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64228,7 +64228,7 @@
         <v>45370</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64301,7 +64301,7 @@
         <v>45246</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64374,7 +64374,7 @@
         <v>45357</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64447,7 +64447,7 @@
         <v>45367</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64520,7 +64520,7 @@
         <v>45673</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64593,7 +64593,7 @@
         <v>45301</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64666,7 +64666,7 @@
         <v>45625</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
         <v>45489</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64812,7 +64812,7 @@
         <v>45785</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>45786</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64958,7 +64958,7 @@
         <v>45401</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65031,7 +65031,7 @@
         <v>45534</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65104,7 +65104,7 @@
         <v>44665</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65177,7 +65177,7 @@
         <v>44592</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65250,7 +65250,7 @@
         <v>44587</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65323,7 +65323,7 @@
         <v>44594</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65396,7 +65396,7 @@
         <v>44693</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65469,7 +65469,7 @@
         <v>44587</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65542,7 +65542,7 @@
         <v>44973</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65615,7 +65615,7 @@
         <v>45422</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65688,7 +65688,7 @@
         <v>45649</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65761,7 +65761,7 @@
         <v>45457</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65834,7 +65834,7 @@
         <v>45088</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65907,7 +65907,7 @@
         <v>45469</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65980,7 +65980,7 @@
         <v>45000</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66053,7 +66053,7 @@
         <v>45224</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66126,7 +66126,7 @@
         <v>45572</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66199,7 +66199,7 @@
         <v>45056</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66272,7 +66272,7 @@
         <v>45558</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66345,7 +66345,7 @@
         <v>44806</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66418,7 +66418,7 @@
         <v>45649</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66491,7 +66491,7 @@
         <v>45056</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66564,7 +66564,7 @@
         <v>45649</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66637,7 +66637,7 @@
         <v>45357</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66710,7 +66710,7 @@
         <v>45088</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66783,7 +66783,7 @@
         <v>45335</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66856,7 +66856,7 @@
         <v>45231</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66929,7 +66929,7 @@
         <v>45572</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67002,7 +67002,7 @@
         <v>45056</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67075,7 +67075,7 @@
         <v>45750</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67148,7 +67148,7 @@
         <v>45847</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67221,7 +67221,7 @@
         <v>45923</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67294,7 +67294,7 @@
         <v>45919</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67367,7 +67367,7 @@
         <v>45926</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67440,7 +67440,7 @@
         <v>45982</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67513,7 +67513,7 @@
         <v>45982</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67586,7 +67586,7 @@
         <v>46030</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67659,7 +67659,7 @@
         <v>46244</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -601,7 +601,7 @@
         <v>46153</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>43929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>46153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45568</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45889</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45730</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45358</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44606</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>44839</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>46153</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44504</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>45561</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>46153</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>46153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>46211</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>45643</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45999</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>46153</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>45189</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>46164</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>46210</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>46247</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45093</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44628</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>45056</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45695</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>45352</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45652</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45888</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>45042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>46126</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>46126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45316</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44656</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>46058</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>44748</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44853</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>44593</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>45110</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>46009</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45222</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>45888</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45188</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>45446</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>44785</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>45818</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>45604</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>45850</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>45075</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>46141</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44869</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>45154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44917</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>44937</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>45174</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45104</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44980</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>45093</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>45447</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44853</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>45335</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44595</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>44607</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44860</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45813</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44612</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>45594</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>45547</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>46002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>46002</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45898</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>44966</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45111</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44917</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>46057</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45940</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44951</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>46094</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45279</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>46109</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>46126</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45616</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>46141</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>45649</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45758</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>46153</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>46153</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>46153</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>46169</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>45096</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>46183</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45069</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45449</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>46190</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44648</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44882</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44908</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>45155</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>45215</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>46230</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>45545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>45581</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>45118</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>46153</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>46254</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44798</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>45730</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>45307</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>45541</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45701</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44909</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44592</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>44830</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45572</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>44603</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>44590</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>46293</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>44491</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44630</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>44889</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>44691</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>44474</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>44861</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>44475</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>44473</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>44581</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>44844</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>44816</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44571</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44645</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44565</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44831</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44783</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44566</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>44684</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>44806</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>44493</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>44488</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>44833</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>44624</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>44776</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>44870</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>44771</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>44657</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44612</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>44617</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>44551</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>44508</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>44851</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44629</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44494</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>44881</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44796</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44551</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44593</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44813</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>44785</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>44650</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44839</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>44805</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>44593</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44526</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44578</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44634</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44634</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44727</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>44551</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44870</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>44587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45273</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45341</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45022</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45775</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>45488</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>45103</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>45649</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>45649</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>44489</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>45230</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>45092</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44819</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45054</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45123</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>45162</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45075</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45091</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>44657</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45181</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45606</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>44973</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>44544</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>44818</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45278</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45175</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44933</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45028</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44692</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>44985</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45561</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>45763</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45625</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45706</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45786</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45307</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45394</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45673</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45572</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45665</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45534</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45603</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45111</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45357</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45301</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45401</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45021</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45367</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44982</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45376</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45037</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45246</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45370</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45327</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>44936</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45849</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45791</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45849</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45098</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45253</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>44973</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45728</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45685</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>44609</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45791</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45698</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>44909</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>44909</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45888</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>45628</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44494</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>46000</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45448</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45118</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>44594</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>46029</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45894</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>45894</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45729</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45107</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45798</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45149</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>46034</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>45852</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45189</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45908</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>44833</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45075</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45840</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45260</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45701</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45761</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45761</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45106</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>44697</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45547</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45917</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>46051</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45525</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>44882</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45049</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45222</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45121</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45366</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45923</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45260</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45926</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>45346</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>44992</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45409</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>46064</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>46064</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>44928</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>44690</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>46069</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44778</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46069</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>46067</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>45938</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>45664</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>44867</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>45338</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>46072</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45484</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>46072</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46072</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45407</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>44959</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>46078</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45945</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>44949</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45946</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45946</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45063</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45254</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>44959</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>45188</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>46083</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>46083</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>44915</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28477,7 +28477,7 @@
         <v>45394</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45525</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>44721</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>46086</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45812</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45958</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>44903</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45368</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45369</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>45958</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>45958</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45958</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>46087</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>44853</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>46092</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>46092</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>44890</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45429</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45331</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45561</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45223</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45210</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45561</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>44497</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45091</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>46104</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45240</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>44914</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44914</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>44931</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>46106</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45975</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>46106</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>45096</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>45359</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45818</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>45980</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>45980</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45980</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>46112</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>45985</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>46112</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>46112</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>45821</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>46113</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>45986</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45986</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>45987</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>45825</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>44832</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45824</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44733</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>45103</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>45694</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>45824</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32542,7 +32542,7 @@
         <v>46122</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>46122</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>45191</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>44865</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>45217</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>46125</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>46125</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>46127</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>45145</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>45145</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>45999</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>45163</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>45182</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33496,7 +33496,7 @@
         <v>46127</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>46000</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44819</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>46133</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>44867</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33866,7 +33866,7 @@
         <v>44528</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45833</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>46133</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34085,7 +34085,7 @@
         <v>45091</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45169</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>45233</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>45392</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>46134</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>46134</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45103</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45103</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>46134</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>45834</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>45834</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>45705</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>45834</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>45342</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>45834</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>45321</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>45649</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>46078</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>45213</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>44868</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>45980</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45478</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>46139</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>45629</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45135</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45644</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>44945</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45837</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45837</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>45551</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45931</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45211</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45762</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45363</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45077</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45616</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45616</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45637</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>44811</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45931</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>46058</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45817</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45946</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45572</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45846</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45846</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>45096</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>45966</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45216</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>44909</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>44991</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>45069</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45679</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>44973</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45975</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>44684</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>46052</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>44974</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>45713</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>45057</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45057</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45852</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>44972</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>45606</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>45577</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45478</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>45859</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45914</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>45930</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45856</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45217</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45951</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>45174</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45856</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>45385</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45862</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45011</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>45966</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44645</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45820</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45841</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45400</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>45832</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45231</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40262,7 +40262,7 @@
         <v>45610</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45887</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>46141</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>45534</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>45055</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40632,7 +40632,7 @@
         <v>45744</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45714</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>45327</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>45664</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>46141</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>45253</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>45411</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41148,7 +41148,7 @@
         <v>45191</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>46141</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45818</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>45474</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>45649</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>45616</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>45649</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45762</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>44917</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44938</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>45392</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45560</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>44867</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45280</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44580</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45591</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45043</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>45616</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45426</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>45050</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45330</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45103</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>44974</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>44693</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>44739</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>44494</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>45296</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45187</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
         <v>44586</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>46153</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>44904</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>46153</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>44798</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45733</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>45415</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>44977</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>45035</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43884,7 +43884,7 @@
         <v>44909</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45090</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>46155</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44103,7 +44103,7 @@
         <v>44621</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>44579</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>45372</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>44803</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>46057</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45894</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>44904</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>44904</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         <v>45560</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>45079</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>45763</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44906,7 +44906,7 @@
         <v>45197</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45469</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>46160</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45478</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45198,7 +45198,7 @@
         <v>44939</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>45313</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45079</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45881</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>45880</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>46168</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45880</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>45090</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45756</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45342</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>44908</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>45561</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45090</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46157,7 +46157,7 @@
         <v>45110</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45670</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45882</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46386,7 +46386,7 @@
         <v>45882</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45883</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45078</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>45013</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46678,7 +46678,7 @@
         <v>45883</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45737</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46824,7 +46824,7 @@
         <v>46175</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>46169</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46970,7 +46970,7 @@
         <v>46178</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47043,7 +47043,7 @@
         <v>45603</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>44505</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>44900</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>45253</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>45072</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45603</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>46181</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47559,7 +47559,7 @@
         <v>45169</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45166</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>46177</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>45407</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>46178</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47929,7 +47929,7 @@
         <v>44970</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45763</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45477</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48148,7 +48148,7 @@
         <v>45551</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48221,7 +48221,7 @@
         <v>44868</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>46182</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48372,7 +48372,7 @@
         <v>46184</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45728</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>44866</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48596,7 +48596,7 @@
         <v>46184</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45196</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48742,7 +48742,7 @@
         <v>45190</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48815,7 +48815,7 @@
         <v>45408</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48888,7 +48888,7 @@
         <v>46190</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>46190</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49034,7 +49034,7 @@
         <v>45369</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>44957</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>44957</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49253,7 +49253,7 @@
         <v>45695</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45013</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>45552</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49472,7 +49472,7 @@
         <v>45149</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49545,7 +49545,7 @@
         <v>45440</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45082</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>44973</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45092</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>44999</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49920,7 +49920,7 @@
         <v>46197</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>46197</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>44841</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>46197</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>45121</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>46198</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>45575</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>45072</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50519,7 +50519,7 @@
         <v>45022</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45470</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50665,7 +50665,7 @@
         <v>44959</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50738,7 +50738,7 @@
         <v>46199</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>44839</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         <v>45369</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45093</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51030,7 +51030,7 @@
         <v>45463</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>45093</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51176,7 +51176,7 @@
         <v>45121</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45561</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51327,7 +51327,7 @@
         <v>45561</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>44746</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45439</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>45075</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>46205</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>45070</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>45244</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51843,7 +51843,7 @@
         <v>44881</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51916,7 +51916,7 @@
         <v>45740</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51989,7 +51989,7 @@
         <v>44873</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>45084</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52135,7 +52135,7 @@
         <v>44973</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45442</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>45336</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>44844</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52427,7 +52427,7 @@
         <v>45079</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52500,7 +52500,7 @@
         <v>45315</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45341</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45509</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52719,7 +52719,7 @@
         <v>45510</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52792,7 +52792,7 @@
         <v>44713</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52865,7 +52865,7 @@
         <v>45367</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52938,7 +52938,7 @@
         <v>45635</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45475</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>45475</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53157,7 +53157,7 @@
         <v>44825</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>46261</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53303,7 +53303,7 @@
         <v>45666</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>44497</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>45554</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53527,7 +53527,7 @@
         <v>45071</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53600,7 +53600,7 @@
         <v>45117</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53673,7 +53673,7 @@
         <v>45356</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53746,7 +53746,7 @@
         <v>45175</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>44953</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53892,7 +53892,7 @@
         <v>45335</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45335</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54043,7 +54043,7 @@
         <v>45218</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>45093</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45078</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54262,7 +54262,7 @@
         <v>44816</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54335,7 +54335,7 @@
         <v>44928</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54408,7 +54408,7 @@
         <v>46269</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54481,7 +54481,7 @@
         <v>46269</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54554,7 +54554,7 @@
         <v>45414</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54627,7 +54627,7 @@
         <v>44713</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54700,7 +54700,7 @@
         <v>46272</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>46273</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>45385</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>46274</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>44889</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>45111</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45131</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>46275</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55289,7 +55289,7 @@
         <v>46279</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55362,7 +55362,7 @@
         <v>46279</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>44756</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45063</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>44874</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55659,7 +55659,7 @@
         <v>46238</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>45119</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>44677</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55883,7 +55883,7 @@
         <v>46238</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55961,7 +55961,7 @@
         <v>45198</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56034,7 +56034,7 @@
         <v>45301</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>45301</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>45512</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56253,7 +56253,7 @@
         <v>44742</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56326,7 +56326,7 @@
         <v>46282</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>46283</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56472,7 +56472,7 @@
         <v>45359</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>44713</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>45096</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56691,7 +56691,7 @@
         <v>45590</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56764,7 +56764,7 @@
         <v>44798</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56837,7 +56837,7 @@
         <v>46175</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56910,7 +56910,7 @@
         <v>44593</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56983,7 +56983,7 @@
         <v>45098</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45392</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>44746</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>46286</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57275,7 +57275,7 @@
         <v>45056</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>46241</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>45744</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45118</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57567,7 +57567,7 @@
         <v>46246</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         <v>45056</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57713,7 +57713,7 @@
         <v>45544</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57786,7 +57786,7 @@
         <v>44827</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>46246</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57932,7 +57932,7 @@
         <v>45016</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>44825</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58078,7 +58078,7 @@
         <v>46289</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58151,7 +58151,7 @@
         <v>46134</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58224,7 +58224,7 @@
         <v>44594</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45095</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45244</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58443,7 +58443,7 @@
         <v>46250</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58516,7 +58516,7 @@
         <v>46248</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58589,7 +58589,7 @@
         <v>45211</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58662,7 +58662,7 @@
         <v>45367</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58735,7 +58735,7 @@
         <v>45938</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>45792</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58886,7 +58886,7 @@
         <v>45072</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58959,7 +58959,7 @@
         <v>45244</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>44999</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59105,7 +59105,7 @@
         <v>45188</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45342</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59251,7 +59251,7 @@
         <v>46295</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59324,7 +59324,7 @@
         <v>44910</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59397,7 +59397,7 @@
         <v>46112</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         <v>45156</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59543,7 +59543,7 @@
         <v>44566</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59616,7 +59616,7 @@
         <v>45373</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59689,7 +59689,7 @@
         <v>46255</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59767,7 +59767,7 @@
         <v>45210</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59840,7 +59840,7 @@
         <v>46253</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59918,7 +59918,7 @@
         <v>44909</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59991,7 +59991,7 @@
         <v>44909</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60064,7 +60064,7 @@
         <v>46246</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60137,7 +60137,7 @@
         <v>45668</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         <v>45940</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60283,7 +60283,7 @@
         <v>45156</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60356,7 +60356,7 @@
         <v>46252</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60429,7 +60429,7 @@
         <v>46254</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>44866</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60580,7 +60580,7 @@
         <v>46297</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60653,7 +60653,7 @@
         <v>44755</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60726,7 +60726,7 @@
         <v>44594</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60799,7 +60799,7 @@
         <v>44992</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60872,7 +60872,7 @@
         <v>46029</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>46255</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>46253</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>45373</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61169,7 +61169,7 @@
         <v>45085</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61242,7 +61242,7 @@
         <v>45475</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61315,7 +61315,7 @@
         <v>45205</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61388,7 +61388,7 @@
         <v>45401</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61461,7 +61461,7 @@
         <v>45239</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61534,7 +61534,7 @@
         <v>45089</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>45079</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>45429</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61758,7 +61758,7 @@
         <v>45762</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61831,7 +61831,7 @@
         <v>44785</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61904,7 +61904,7 @@
         <v>45113</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61977,7 +61977,7 @@
         <v>44880</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>44488</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45089</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62196,7 +62196,7 @@
         <v>45208</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62269,7 +62269,7 @@
         <v>45534</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62342,7 +62342,7 @@
         <v>45342</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62415,7 +62415,7 @@
         <v>45484</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62488,7 +62488,7 @@
         <v>45706</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62561,7 +62561,7 @@
         <v>45756</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62634,7 +62634,7 @@
         <v>44700</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62707,7 +62707,7 @@
         <v>44622</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>45240</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62853,7 +62853,7 @@
         <v>44865</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62926,7 +62926,7 @@
         <v>45761</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63004,7 +63004,7 @@
         <v>44749</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63077,7 +63077,7 @@
         <v>44973</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63150,7 +63150,7 @@
         <v>45175</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63223,7 +63223,7 @@
         <v>45308</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63296,7 +63296,7 @@
         <v>45149</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63369,7 +63369,7 @@
         <v>45210</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63442,7 +63442,7 @@
         <v>44881</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63515,7 +63515,7 @@
         <v>45175</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63588,7 +63588,7 @@
         <v>45371</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63661,7 +63661,7 @@
         <v>44743</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63734,7 +63734,7 @@
         <v>44594</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63807,7 +63807,7 @@
         <v>45320</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63880,7 +63880,7 @@
         <v>45741</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63953,7 +63953,7 @@
         <v>45681</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64031,7 +64031,7 @@
         <v>44882</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64104,7 +64104,7 @@
         <v>45679</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45586</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64250,7 +64250,7 @@
         <v>44606</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64323,7 +64323,7 @@
         <v>45545</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64396,7 +64396,7 @@
         <v>45449</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64469,7 +64469,7 @@
         <v>45070</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64542,7 +64542,7 @@
         <v>45601</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64615,7 +64615,7 @@
         <v>45476</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64688,7 +64688,7 @@
         <v>45489</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64761,7 +64761,7 @@
         <v>45587</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64834,7 +64834,7 @@
         <v>45785</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64907,7 +64907,7 @@
         <v>45230</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64980,7 +64980,7 @@
         <v>45489</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65053,7 +65053,7 @@
         <v>44665</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65126,7 +65126,7 @@
         <v>44973</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65199,7 +65199,7 @@
         <v>45422</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65272,7 +65272,7 @@
         <v>45649</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65345,7 +65345,7 @@
         <v>45457</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65418,7 +65418,7 @@
         <v>45088</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65491,7 +65491,7 @@
         <v>45469</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65564,7 +65564,7 @@
         <v>45000</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65637,7 +65637,7 @@
         <v>45224</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65710,7 +65710,7 @@
         <v>45572</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65783,7 +65783,7 @@
         <v>45056</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65856,7 +65856,7 @@
         <v>44592</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65929,7 +65929,7 @@
         <v>45558</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66002,7 +66002,7 @@
         <v>44587</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66075,7 +66075,7 @@
         <v>44806</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66148,7 +66148,7 @@
         <v>45649</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66221,7 +66221,7 @@
         <v>45056</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66294,7 +66294,7 @@
         <v>45649</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66367,7 +66367,7 @@
         <v>44594</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66440,7 +66440,7 @@
         <v>44693</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66513,7 +66513,7 @@
         <v>45357</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45088</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66659,7 +66659,7 @@
         <v>45335</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66732,7 +66732,7 @@
         <v>45231</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66805,7 +66805,7 @@
         <v>44587</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66878,7 +66878,7 @@
         <v>45572</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66951,7 +66951,7 @@
         <v>45056</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67024,7 +67024,7 @@
         <v>45750</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67097,7 +67097,7 @@
         <v>45847</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67170,7 +67170,7 @@
         <v>45923</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67243,7 +67243,7 @@
         <v>45919</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67316,7 +67316,7 @@
         <v>45926</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>45982</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67462,7 +67462,7 @@
         <v>45982</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67535,7 +67535,7 @@
         <v>46030</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67608,7 +67608,7 @@
         <v>46244</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67681,7 +67681,7 @@
         <v>46295</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -601,7 +601,7 @@
         <v>46153</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>43929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>46153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45568</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45889</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45730</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45358</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44606</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>44839</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>46153</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44504</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>45561</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>46153</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>46153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>46211</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>44867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>45643</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45999</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>46153</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>45189</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>46164</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>46210</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>46247</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45093</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44628</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>45056</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45695</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>45352</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45652</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45888</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>45042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>46126</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>46126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45316</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44656</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>46058</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>44748</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44853</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>44593</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>45110</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>46009</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45222</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>45888</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45188</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>45446</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>44785</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>45818</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>45604</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>45850</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>45075</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>46141</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44869</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>45154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44917</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>44937</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>45174</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45104</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44980</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>45093</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>45447</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44853</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>45335</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44595</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>44607</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44860</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45813</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44612</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>45594</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>45547</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>46002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>46002</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45898</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>44966</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45111</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44917</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>46057</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45940</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44951</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>46094</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45279</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>46109</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>46126</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45616</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>46141</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>45649</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45758</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>46153</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>46153</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>46153</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>46169</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>45096</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>46183</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45069</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45449</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>46190</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44648</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44882</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44908</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>45155</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>45215</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>46230</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>45545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>45581</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>45118</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>46153</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>46254</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44798</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>45730</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>45307</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>45541</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45701</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44909</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44592</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>44830</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45572</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>44603</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>44590</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>46293</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>44491</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44630</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>44889</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>44691</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>44474</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>44861</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>44475</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>44473</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>44581</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>44844</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>44816</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44571</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44645</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44565</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44831</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44783</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44566</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>44684</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>44806</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>44493</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>44488</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>44833</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>44624</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>44776</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>44870</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>44771</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>44657</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44612</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>44617</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>44551</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>44508</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>44851</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44629</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44494</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>44881</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44796</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44551</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44593</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44813</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>44785</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>44650</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44839</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>44805</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>44593</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44526</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44578</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44634</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44634</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44727</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>44551</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44870</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>44587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45273</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45341</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45022</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45775</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>45488</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>45103</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>45649</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>45649</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>44489</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>45230</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>45092</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44819</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45054</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45123</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>45162</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45075</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45091</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>44657</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45181</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45606</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>44973</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>44544</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>44818</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45278</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45175</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44933</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45028</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44692</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>44985</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45561</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>45763</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45625</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45706</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45786</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45307</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45394</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45673</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45572</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45665</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45534</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45603</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45111</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45357</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45301</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45401</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45021</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45367</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44982</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45376</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45037</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45246</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45370</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45327</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>44936</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45849</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45791</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45849</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45098</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45253</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>44973</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45728</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45685</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>44609</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45791</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45698</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>44909</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>44909</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45888</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>45628</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44494</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>46000</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45448</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45118</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>44594</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>46029</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45894</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>45894</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45729</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45107</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45798</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45149</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>46034</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>45852</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45189</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45908</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>44833</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45075</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45840</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45260</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45701</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45761</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45761</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45106</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>44697</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45547</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45917</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>46051</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45525</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>44882</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45049</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45222</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45121</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45366</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45923</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45260</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45926</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>45346</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>44992</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45409</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>46064</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>46064</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>44928</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>44690</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>46069</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44778</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46069</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>46067</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>45938</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>45664</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>44867</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>45338</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>46072</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45484</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>46072</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46072</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45407</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>44959</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>46078</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45945</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>44949</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45946</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45946</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45063</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45254</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>44959</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>45188</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>46083</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>46083</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>44915</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28477,7 +28477,7 @@
         <v>45394</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45525</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>44721</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>46086</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45812</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45958</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>44903</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45368</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45369</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>45958</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>45958</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45958</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>46087</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>44853</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>46092</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>46092</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>44890</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45429</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45331</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45561</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45223</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45210</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45561</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>44497</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45091</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>46104</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45240</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>44914</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44914</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>44931</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>46106</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45975</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>46106</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>45096</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>45359</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45818</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>45980</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>45980</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45980</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>46112</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>45985</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>46112</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>46112</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>45821</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>46113</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>45986</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45986</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>45987</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>45825</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>44832</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45824</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44733</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>45103</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>45694</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>45824</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32542,7 +32542,7 @@
         <v>46122</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>46122</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>45191</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>44865</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>45217</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>46125</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>46125</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>46127</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>45145</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>45145</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>45999</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>45163</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>45182</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33496,7 +33496,7 @@
         <v>46127</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>46000</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44819</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>46133</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>44867</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33866,7 +33866,7 @@
         <v>44528</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45833</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>46133</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34085,7 +34085,7 @@
         <v>45091</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45169</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>45233</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>45392</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>46134</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>46134</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45103</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45103</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>46134</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>45834</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>45834</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>45705</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>45834</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>45342</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>45834</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>45321</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>45649</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>46078</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>45213</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>44868</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>45980</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45478</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>46139</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>45629</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45135</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45644</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>44945</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45837</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45837</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>45551</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45931</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45211</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45762</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45363</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45077</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45616</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45616</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45637</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>44811</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45931</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>46058</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45817</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45946</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45572</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45846</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45846</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>45096</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>45966</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45216</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>44909</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>44991</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>45069</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45679</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>44973</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45975</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>44684</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>46052</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>44974</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>45713</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>45057</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45057</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45852</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>44972</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>45606</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>45577</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45478</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>45859</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45914</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>45930</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45856</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45217</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45951</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>45174</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45856</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>45385</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45862</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45011</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>45966</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44645</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45820</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45841</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45400</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>45832</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45231</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40262,7 +40262,7 @@
         <v>45610</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45887</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>46141</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>45534</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>45055</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40632,7 +40632,7 @@
         <v>45744</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45714</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>45327</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>45664</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>46141</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>45253</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>45411</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41148,7 +41148,7 @@
         <v>45191</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>46141</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45818</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>45474</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>45649</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>45616</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>45649</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45762</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>44917</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44938</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>45392</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45560</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>44867</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45280</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44580</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45591</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45043</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>45616</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45426</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>45050</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45330</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45103</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>44974</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>44693</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>44739</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>44494</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>45296</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45187</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
         <v>44586</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>46153</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>44904</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>46153</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>44798</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45733</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>45415</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>44977</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>45035</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43884,7 +43884,7 @@
         <v>44909</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45090</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>46155</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44103,7 +44103,7 @@
         <v>44621</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>44579</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>45372</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>44803</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>46057</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45894</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>44904</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>44904</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         <v>45560</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>45079</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>45763</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44906,7 +44906,7 @@
         <v>45197</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45469</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>46160</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45478</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45198,7 +45198,7 @@
         <v>44939</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>45313</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45079</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45881</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>45880</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>46168</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45880</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>45090</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45756</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45342</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>44908</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>45561</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45090</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46157,7 +46157,7 @@
         <v>45110</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45670</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45882</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46386,7 +46386,7 @@
         <v>45882</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45883</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45078</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>45013</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46678,7 +46678,7 @@
         <v>45883</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45737</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46824,7 +46824,7 @@
         <v>46175</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>46169</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46970,7 +46970,7 @@
         <v>46178</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47043,7 +47043,7 @@
         <v>45603</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>44505</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>44900</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>45253</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>45072</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45603</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>46181</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47559,7 +47559,7 @@
         <v>45169</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45166</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>46177</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>45407</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>46178</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47929,7 +47929,7 @@
         <v>44970</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45763</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45477</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48148,7 +48148,7 @@
         <v>45551</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48221,7 +48221,7 @@
         <v>44868</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>46182</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48372,7 +48372,7 @@
         <v>46184</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45728</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>44866</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48596,7 +48596,7 @@
         <v>46184</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45196</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48742,7 +48742,7 @@
         <v>45190</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48815,7 +48815,7 @@
         <v>45408</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48888,7 +48888,7 @@
         <v>46190</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>46190</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49034,7 +49034,7 @@
         <v>45369</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>44957</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>44957</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49253,7 +49253,7 @@
         <v>45695</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45013</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>45552</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49472,7 +49472,7 @@
         <v>45149</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49545,7 +49545,7 @@
         <v>45440</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45082</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>44973</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45092</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>44999</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49920,7 +49920,7 @@
         <v>46197</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>46197</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>44841</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>46197</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>45121</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>46198</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>45575</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>45072</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50519,7 +50519,7 @@
         <v>45022</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45470</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50665,7 +50665,7 @@
         <v>44959</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50738,7 +50738,7 @@
         <v>46199</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>44839</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         <v>45369</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45093</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51030,7 +51030,7 @@
         <v>45463</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>45093</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51176,7 +51176,7 @@
         <v>45121</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45561</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51327,7 +51327,7 @@
         <v>45561</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>44746</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45439</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>45075</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>46205</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>45070</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>45244</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51843,7 +51843,7 @@
         <v>44881</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51916,7 +51916,7 @@
         <v>45740</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51989,7 +51989,7 @@
         <v>44873</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>45084</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52135,7 +52135,7 @@
         <v>44973</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45442</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>45336</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>44844</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52427,7 +52427,7 @@
         <v>45079</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52500,7 +52500,7 @@
         <v>45315</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45341</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45509</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52719,7 +52719,7 @@
         <v>45510</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52792,7 +52792,7 @@
         <v>44713</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52865,7 +52865,7 @@
         <v>45367</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52938,7 +52938,7 @@
         <v>45635</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45475</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>45475</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53157,7 +53157,7 @@
         <v>44825</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>46261</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53303,7 +53303,7 @@
         <v>45666</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>44497</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>45554</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53527,7 +53527,7 @@
         <v>45071</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53600,7 +53600,7 @@
         <v>45117</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53673,7 +53673,7 @@
         <v>45356</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53746,7 +53746,7 @@
         <v>45175</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>44953</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53892,7 +53892,7 @@
         <v>45335</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45335</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54043,7 +54043,7 @@
         <v>45218</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>45093</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45078</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54262,7 +54262,7 @@
         <v>44816</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54335,7 +54335,7 @@
         <v>44928</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54408,7 +54408,7 @@
         <v>46269</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54481,7 +54481,7 @@
         <v>46269</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54554,7 +54554,7 @@
         <v>45414</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54627,7 +54627,7 @@
         <v>44713</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54700,7 +54700,7 @@
         <v>46272</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>46273</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>45385</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>46274</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>44889</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>45111</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45131</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>46275</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55289,7 +55289,7 @@
         <v>46279</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55362,7 +55362,7 @@
         <v>46279</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>44756</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45063</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>44874</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55659,7 +55659,7 @@
         <v>46238</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>45119</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>44677</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55883,7 +55883,7 @@
         <v>46238</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55961,7 +55961,7 @@
         <v>45198</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56034,7 +56034,7 @@
         <v>45301</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>45301</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>45512</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56253,7 +56253,7 @@
         <v>44742</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56326,7 +56326,7 @@
         <v>46282</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>46283</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56472,7 +56472,7 @@
         <v>45359</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>44713</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>45096</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56691,7 +56691,7 @@
         <v>45590</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56764,7 +56764,7 @@
         <v>44798</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56837,7 +56837,7 @@
         <v>46175</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56910,7 +56910,7 @@
         <v>44593</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56983,7 +56983,7 @@
         <v>45098</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45392</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>44746</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>46286</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57275,7 +57275,7 @@
         <v>45056</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>46241</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>45744</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45118</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57567,7 +57567,7 @@
         <v>46246</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         <v>45056</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57713,7 +57713,7 @@
         <v>45544</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57786,7 +57786,7 @@
         <v>44827</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>46246</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57932,7 +57932,7 @@
         <v>45016</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>44825</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58078,7 +58078,7 @@
         <v>46289</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58151,7 +58151,7 @@
         <v>46134</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58224,7 +58224,7 @@
         <v>44594</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45095</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45244</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58443,7 +58443,7 @@
         <v>46250</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58516,7 +58516,7 @@
         <v>46248</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58589,7 +58589,7 @@
         <v>45211</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58662,7 +58662,7 @@
         <v>45367</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58735,7 +58735,7 @@
         <v>45938</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>45792</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58886,7 +58886,7 @@
         <v>45072</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58959,7 +58959,7 @@
         <v>45244</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>44999</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59105,7 +59105,7 @@
         <v>45188</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45342</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59251,7 +59251,7 @@
         <v>46295</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59324,7 +59324,7 @@
         <v>44910</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59397,7 +59397,7 @@
         <v>46112</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59470,7 +59470,7 @@
         <v>45156</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59543,7 +59543,7 @@
         <v>44566</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59616,7 +59616,7 @@
         <v>45373</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59689,7 +59689,7 @@
         <v>46255</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59767,7 +59767,7 @@
         <v>45210</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59840,7 +59840,7 @@
         <v>46253</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59918,7 +59918,7 @@
         <v>44909</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59991,7 +59991,7 @@
         <v>44909</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60064,7 +60064,7 @@
         <v>46246</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60137,7 +60137,7 @@
         <v>45668</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         <v>45940</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60283,7 +60283,7 @@
         <v>45156</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60356,7 +60356,7 @@
         <v>46252</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60429,7 +60429,7 @@
         <v>46254</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>44866</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60580,7 +60580,7 @@
         <v>46297</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60653,7 +60653,7 @@
         <v>44755</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60726,7 +60726,7 @@
         <v>44594</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60799,7 +60799,7 @@
         <v>44992</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60872,7 +60872,7 @@
         <v>46029</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>46255</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>46253</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>45373</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61169,7 +61169,7 @@
         <v>45085</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61242,7 +61242,7 @@
         <v>45475</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61315,7 +61315,7 @@
         <v>45205</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61388,7 +61388,7 @@
         <v>45401</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61461,7 +61461,7 @@
         <v>45239</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61534,7 +61534,7 @@
         <v>45089</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>45079</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>45429</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61758,7 +61758,7 @@
         <v>45762</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61831,7 +61831,7 @@
         <v>44785</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61904,7 +61904,7 @@
         <v>45113</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61977,7 +61977,7 @@
         <v>44880</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>44488</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45089</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62196,7 +62196,7 @@
         <v>45208</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62269,7 +62269,7 @@
         <v>45534</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62342,7 +62342,7 @@
         <v>45342</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62415,7 +62415,7 @@
         <v>45484</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62488,7 +62488,7 @@
         <v>45706</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62561,7 +62561,7 @@
         <v>45756</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62634,7 +62634,7 @@
         <v>44700</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62707,7 +62707,7 @@
         <v>44622</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>45240</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62853,7 +62853,7 @@
         <v>44865</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62926,7 +62926,7 @@
         <v>45761</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63004,7 +63004,7 @@
         <v>44749</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63077,7 +63077,7 @@
         <v>44973</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63150,7 +63150,7 @@
         <v>45175</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63223,7 +63223,7 @@
         <v>45308</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63296,7 +63296,7 @@
         <v>45149</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63369,7 +63369,7 @@
         <v>45210</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63442,7 +63442,7 @@
         <v>44881</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63515,7 +63515,7 @@
         <v>45175</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63588,7 +63588,7 @@
         <v>45371</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63661,7 +63661,7 @@
         <v>44743</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63734,7 +63734,7 @@
         <v>44594</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63807,7 +63807,7 @@
         <v>45320</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63880,7 +63880,7 @@
         <v>45741</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63953,7 +63953,7 @@
         <v>45681</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64031,7 +64031,7 @@
         <v>44882</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64104,7 +64104,7 @@
         <v>45679</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45586</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64250,7 +64250,7 @@
         <v>44606</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64323,7 +64323,7 @@
         <v>45545</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64396,7 +64396,7 @@
         <v>45449</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64469,7 +64469,7 @@
         <v>45070</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64542,7 +64542,7 @@
         <v>45601</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64615,7 +64615,7 @@
         <v>45476</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64688,7 +64688,7 @@
         <v>45489</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64761,7 +64761,7 @@
         <v>45587</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64834,7 +64834,7 @@
         <v>45785</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64907,7 +64907,7 @@
         <v>45230</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64980,7 +64980,7 @@
         <v>45489</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65053,7 +65053,7 @@
         <v>44665</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65126,7 +65126,7 @@
         <v>44973</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65199,7 +65199,7 @@
         <v>45422</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65272,7 +65272,7 @@
         <v>45649</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65345,7 +65345,7 @@
         <v>45457</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65418,7 +65418,7 @@
         <v>45088</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65491,7 +65491,7 @@
         <v>45469</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65564,7 +65564,7 @@
         <v>45000</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65637,7 +65637,7 @@
         <v>45224</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65710,7 +65710,7 @@
         <v>45572</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65783,7 +65783,7 @@
         <v>45056</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65856,7 +65856,7 @@
         <v>44592</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65929,7 +65929,7 @@
         <v>45558</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66002,7 +66002,7 @@
         <v>44587</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66075,7 +66075,7 @@
         <v>44806</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66148,7 +66148,7 @@
         <v>45649</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66221,7 +66221,7 @@
         <v>45056</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66294,7 +66294,7 @@
         <v>45649</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66367,7 +66367,7 @@
         <v>44594</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66440,7 +66440,7 @@
         <v>44693</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66513,7 +66513,7 @@
         <v>45357</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45088</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66659,7 +66659,7 @@
         <v>45335</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66732,7 +66732,7 @@
         <v>45231</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66805,7 +66805,7 @@
         <v>44587</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66878,7 +66878,7 @@
         <v>45572</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66951,7 +66951,7 @@
         <v>45056</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67024,7 +67024,7 @@
         <v>45750</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67097,7 +67097,7 @@
         <v>45847</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67170,7 +67170,7 @@
         <v>45923</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67243,7 +67243,7 @@
         <v>45919</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67316,7 +67316,7 @@
         <v>45926</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>45982</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67462,7 +67462,7 @@
         <v>45982</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67535,7 +67535,7 @@
         <v>46030</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67608,7 +67608,7 @@
         <v>46244</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67681,7 +67681,7 @@
         <v>46295</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -601,7 +601,7 @@
         <v>46153</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>43929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>46153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45568</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45889</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45730</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45358</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44606</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>44839</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>44504</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>45561</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>44867</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>46153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>46153</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>46211</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>45643</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45189</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>45999</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46153</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>46164</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>46174</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>46210</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46247</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44628</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>45056</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45695</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>45316</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45352</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45042</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>45652</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>44656</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45888</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>46126</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>46058</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>44853</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44748</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>44593</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>45188</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>45174</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>45446</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45447</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45888</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>45104</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45075</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45110</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>45818</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44785</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45093</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45850</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>45154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44869</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>46009</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>45604</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44917</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>45222</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>46141</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44595</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44853</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>45335</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44860</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45813</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44612</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>44602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>44951</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45649</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45215</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44882</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>45279</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45096</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45155</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>45898</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>45545</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>44908</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>45594</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>45541</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44909</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>45547</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>45701</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>45118</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>45758</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>45449</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44648</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>45581</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>45616</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>45307</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>45730</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>46094</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>46109</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44917</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>46002</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>46002</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>44798</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45069</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>45111</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44966</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>46057</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>46141</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>46153</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>46153</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>46153</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>46169</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>46183</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>46190</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>46153</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>46254</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>46300</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>46302</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45940</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>46230</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>44592</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>44603</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>44590</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>44830</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45572</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>46293</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>44491</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>44630</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>44889</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44691</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>44859</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44861</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44581</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44844</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44816</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44571</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44645</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44565</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>44831</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>44783</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44566</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44684</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44493</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44806</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>44488</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>44833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>44587</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>44624</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>44805</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44593</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>44617</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>44526</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44593</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44578</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>44551</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>44508</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>44813</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44776</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>44870</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44851</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>44785</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44771</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>44634</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>44634</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>44657</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44650</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44629</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44494</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44727</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>44839</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44881</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>44796</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44551</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>44866</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>44866</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>44612</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44755</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45763</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44867</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>44551</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45075</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45253</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>44870</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45078</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45342</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44587</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>44827</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45488</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45050</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>45401</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45149</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45075</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45336</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45679</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>44880</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44874</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45013</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45090</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>45091</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45078</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45093</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>45606</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45190</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>44882</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>44586</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45093</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45216</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45341</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45210</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45296</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45162</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44825</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>45342</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45096</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>44865</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44909</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>45103</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>45043</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45054</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>45085</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44890</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45575</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>45308</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45649</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45649</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45240</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45103</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45103</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45156</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45313</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44785</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45376</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45761</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45440</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>44868</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45394</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45011</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45210</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>45368</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45110</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45369</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>45149</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45591</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45635</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45469</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45028</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45478</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45510</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44811</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>44867</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>45359</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45429</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45118</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45121</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45280</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45123</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>44839</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>44594</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45331</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45117</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45791</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>45737</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45022</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45084</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>45253</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>44778</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45056</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45149</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45561</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45561</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44489</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45205</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45849</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45253</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>44973</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44973</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45685</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>45103</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45791</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>44505</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45883</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45883</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45698</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>45603</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>45240</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>45603</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>45603</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>44982</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45233</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44957</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44957</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>44903</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45849</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45477</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45079</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45882</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>45169</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45107</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45407</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44953</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>44936</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>44882</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45156</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44609</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45888</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45628</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>45069</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>45166</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45163</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>45342</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>45373</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>44528</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45369</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>45356</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>45321</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>45429</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>45894</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28299,7 +28299,7 @@
         <v>45894</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>45013</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>45560</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>45341</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28591,7 +28591,7 @@
         <v>45798</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         <v>45475</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45475</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45852</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45096</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45679</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45729</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44938</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>45714</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>44915</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45649</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45649</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45649</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>44973</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45217</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45908</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45762</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>44972</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>44999</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45666</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45840</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45181</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>45089</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45070</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>44606</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45551</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44488</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45601</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45449</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45545</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45744</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45476</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45260</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45489</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>44914</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>45547</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45616</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>45544</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45096</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45474</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>45169</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44580</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45587</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45079</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>45665</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>45706</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>45320</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44904</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45572</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45917</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>45442</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45230</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>44959</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>45370</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>45246</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>45357</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>45113</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>45367</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45673</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>45664</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>45301</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>45625</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45489</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>44928</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45785</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45131</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>44544</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>45763</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>44959</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>45786</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45315</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45401</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45016</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45923</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>45534</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>45561</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>44692</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45561</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45561</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>44566</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45103</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45092</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>45408</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>45197</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>45926</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>44992</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45098</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>44873</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>45035</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>45701</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>45145</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45145</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44593</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44832</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45761</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>45218</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>45335</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45338</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45222</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44973</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45560</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45385</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>44645</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>44910</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45372</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>45037</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44939</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>45223</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45230</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>45367</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45664</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>44697</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>44677</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>45373</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44733</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>44867</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45063</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44970</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45082</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45525</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>45191</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>45191</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44657</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>44594</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>45049</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>44622</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45938</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45095</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>45695</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45637</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>44713</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>45812</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>45415</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45071</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>45072</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45586</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>45439</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>45740</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>45945</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>44825</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>45070</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45367</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45762</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39080,7 +39080,7 @@
         <v>45411</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45118</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45392</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45196</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>45946</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>44713</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>45121</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>45121</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>44746</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>44833</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45818</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>45946</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>44690</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44798</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>45824</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>45307</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45359</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>45821</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>45824</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>44684</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>45089</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>45629</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>44931</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>45182</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40847,7 +40847,7 @@
         <v>45825</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45175</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>45106</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45093</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45244</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41212,7 +41212,7 @@
         <v>45741</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>45057</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>45057</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>45756</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>45958</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41577,7 +41577,7 @@
         <v>45958</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>45958</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45958</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41796,7 +41796,7 @@
         <v>45834</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>45834</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>45834</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>45211</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>44819</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>45833</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45187</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>45834</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42380,7 +42380,7 @@
         <v>45407</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42453,7 +42453,7 @@
         <v>45681</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45239</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>45837</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45837</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>44742</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44909</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42896,7 +42896,7 @@
         <v>45175</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45198</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45210</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
         <v>45475</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>45211</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44749</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>44999</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>44721</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43480,7 +43480,7 @@
         <v>45616</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>44743</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45846</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>45817</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45175</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45846</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45616</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>45414</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>45756</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>44909</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45706</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>45119</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45244</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>45852</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>44841</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45975</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45484</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>45409</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45694</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45775</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>44803</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>44693</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>45856</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>45448</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>45856</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>44739</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>44746</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>45022</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45254</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45818</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45616</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>45330</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>44497</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>44974</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45111</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>45366</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45980</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45231</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45217</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>45980</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>44917</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45980</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46581,7 +46581,7 @@
         <v>44959</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45273</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>44819</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45301</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>45301</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45763</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>44818</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45880</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>45327</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45369</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45762</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>44945</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>44494</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>45733</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47613,7 +47613,7 @@
         <v>45880</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45092</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>45881</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>44991</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45882</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47988,7 +47988,7 @@
         <v>45554</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45346</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>45728</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>44816</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48290,7 +48290,7 @@
         <v>45278</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48363,7 +48363,7 @@
         <v>44881</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>44844</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         <v>45090</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45610</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>44756</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48733,7 +48733,7 @@
         <v>45091</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>45986</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48879,7 +48879,7 @@
         <v>45509</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>44868</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45189</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49103,7 +49103,7 @@
         <v>45985</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>44621</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45728</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45986</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
         <v>45484</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>44865</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49546,7 +49546,7 @@
         <v>46104</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>44700</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>45072</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>46106</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>44985</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>44889</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45135</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>46106</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50140,7 +50140,7 @@
         <v>45463</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50213,7 +50213,7 @@
         <v>45055</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>45534</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45111</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45987</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>45761</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>46113</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>46112</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45426</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45394</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50880,7 +50880,7 @@
         <v>45090</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50953,7 +50953,7 @@
         <v>45342</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51026,7 +51026,7 @@
         <v>46112</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51099,7 +51099,7 @@
         <v>46112</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>45400</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51245,7 +51245,7 @@
         <v>45552</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51318,7 +51318,7 @@
         <v>44909</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>44973</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>46122</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51537,7 +51537,7 @@
         <v>46125</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>46127</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45999</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51756,7 +51756,7 @@
         <v>46000</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51829,7 +51829,7 @@
         <v>46127</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51902,7 +51902,7 @@
         <v>44904</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45174</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45335</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52126,7 +52126,7 @@
         <v>44992</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52199,7 +52199,7 @@
         <v>46133</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52272,7 +52272,7 @@
         <v>44579</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>46134</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>46134</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52491,7 +52491,7 @@
         <v>46134</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52564,7 +52564,7 @@
         <v>44928</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52637,7 +52637,7 @@
         <v>44594</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52710,7 +52710,7 @@
         <v>44933</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>44977</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52856,7 +52856,7 @@
         <v>46133</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52929,7 +52929,7 @@
         <v>44881</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>45478</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53075,7 +53075,7 @@
         <v>45966</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45188</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53221,7 +53221,7 @@
         <v>45363</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45914</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53367,7 +53367,7 @@
         <v>45930</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53445,7 +53445,7 @@
         <v>45244</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53518,7 +53518,7 @@
         <v>45820</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45841</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53669,7 +53669,7 @@
         <v>45072</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53742,7 +53742,7 @@
         <v>45966</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53815,7 +53815,7 @@
         <v>45705</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>45951</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53961,7 +53961,7 @@
         <v>45371</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54034,7 +54034,7 @@
         <v>45478</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54107,7 +54107,7 @@
         <v>44914</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>45577</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54253,7 +54253,7 @@
         <v>45980</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54331,7 +54331,7 @@
         <v>44497</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54404,7 +54404,7 @@
         <v>44949</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54477,7 +54477,7 @@
         <v>45931</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45512</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>45392</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54701,7 +54701,7 @@
         <v>45859</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>45260</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54847,7 +54847,7 @@
         <v>45975</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>45188</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45644</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>45551</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         <v>45931</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>45098</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55290,7 +55290,7 @@
         <v>45862</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>44909</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>45713</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>45385</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>45056</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>45606</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55728,7 +55728,7 @@
         <v>45887</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55801,7 +55801,7 @@
         <v>45075</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55874,7 +55874,7 @@
         <v>45327</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55947,7 +55947,7 @@
         <v>46000</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>46052</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>44900</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56166,7 +56166,7 @@
         <v>45213</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56239,7 +56239,7 @@
         <v>44904</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56312,7 +56312,7 @@
         <v>46029</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56385,7 +56385,7 @@
         <v>44909</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>45077</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56531,7 +56531,7 @@
         <v>45091</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45946</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>44494</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56750,7 +56750,7 @@
         <v>45063</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56823,7 +56823,7 @@
         <v>44798</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56896,7 +56896,7 @@
         <v>44853</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45470</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>45021</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45079</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>45534</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57261,7 +57261,7 @@
         <v>45572</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45668</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>46139</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57480,7 +57480,7 @@
         <v>45832</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>44713</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>46078</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57699,7 +57699,7 @@
         <v>44908</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>44974</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57845,7 +57845,7 @@
         <v>45079</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57918,7 +57918,7 @@
         <v>45208</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57991,7 +57991,7 @@
         <v>45525</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58064,7 +58064,7 @@
         <v>46058</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58137,7 +58137,7 @@
         <v>45590</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58210,7 +58210,7 @@
         <v>45175</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>44973</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58356,7 +58356,7 @@
         <v>46141</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>46051</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58512,7 +58512,7 @@
         <v>46141</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58590,7 +58590,7 @@
         <v>45392</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58663,7 +58663,7 @@
         <v>46141</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>46064</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>46064</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58887,7 +58887,7 @@
         <v>46069</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58960,7 +58960,7 @@
         <v>46067</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59033,7 +59033,7 @@
         <v>46069</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59106,7 +59106,7 @@
         <v>46153</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59184,7 +59184,7 @@
         <v>46072</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59257,7 +59257,7 @@
         <v>46072</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59330,7 +59330,7 @@
         <v>46153</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59408,7 +59408,7 @@
         <v>46078</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59481,7 +59481,7 @@
         <v>46083</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59554,7 +59554,7 @@
         <v>46083</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>46155</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59700,7 +59700,7 @@
         <v>46087</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45894</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59846,7 +59846,7 @@
         <v>46086</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>46160</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59992,7 +59992,7 @@
         <v>46057</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60065,7 +60065,7 @@
         <v>46092</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60138,7 +60138,7 @@
         <v>46092</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60211,7 +60211,7 @@
         <v>46168</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45670</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>46175</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>46169</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         <v>46177</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>46178</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60659,7 +60659,7 @@
         <v>46178</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60732,7 +60732,7 @@
         <v>46184</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60805,7 +60805,7 @@
         <v>46184</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60878,7 +60878,7 @@
         <v>46182</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>46190</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61029,7 +61029,7 @@
         <v>46197</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61107,7 +61107,7 @@
         <v>46197</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>46197</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         <v>46199</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61336,7 +61336,7 @@
         <v>46205</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61409,7 +61409,7 @@
         <v>46269</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61482,7 +61482,7 @@
         <v>46272</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>46269</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61628,7 +61628,7 @@
         <v>46273</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61701,7 +61701,7 @@
         <v>46274</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>46275</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61852,7 +61852,7 @@
         <v>46279</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>46279</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>46282</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         <v>46238</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62149,7 +62149,7 @@
         <v>46238</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62227,7 +62227,7 @@
         <v>46283</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62300,7 +62300,7 @@
         <v>46175</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62373,7 +62373,7 @@
         <v>46241</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62446,7 +62446,7 @@
         <v>45744</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62519,7 +62519,7 @@
         <v>46286</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62592,7 +62592,7 @@
         <v>46134</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62665,7 +62665,7 @@
         <v>46246</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62738,7 +62738,7 @@
         <v>46246</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>45792</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62889,7 +62889,7 @@
         <v>45938</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62962,7 +62962,7 @@
         <v>46289</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63035,7 +63035,7 @@
         <v>44594</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63108,7 +63108,7 @@
         <v>46250</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63181,7 +63181,7 @@
         <v>46248</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>46253</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63332,7 +63332,7 @@
         <v>46295</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63405,7 +63405,7 @@
         <v>46253</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63483,7 +63483,7 @@
         <v>46254</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63561,7 +63561,7 @@
         <v>46300</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63639,7 +63639,7 @@
         <v>46246</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63712,7 +63712,7 @@
         <v>46255</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63790,7 +63790,7 @@
         <v>46112</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>46029</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63936,7 +63936,7 @@
         <v>46255</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>46300</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>46300</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64155,7 +64155,7 @@
         <v>46300</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64228,7 +64228,7 @@
         <v>46300</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64306,7 +64306,7 @@
         <v>46300</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         <v>46297</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64457,7 +64457,7 @@
         <v>46300</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64530,7 +64530,7 @@
         <v>46300</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64603,7 +64603,7 @@
         <v>45940</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64676,7 +64676,7 @@
         <v>46252</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64749,7 +64749,7 @@
         <v>46198</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64822,7 +64822,7 @@
         <v>46302</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64895,7 +64895,7 @@
         <v>46301</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64968,7 +64968,7 @@
         <v>46190</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65041,7 +65041,7 @@
         <v>46301</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65114,7 +65114,7 @@
         <v>46301</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65187,7 +65187,7 @@
         <v>46303</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65260,7 +65260,7 @@
         <v>46295</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65333,7 +65333,7 @@
         <v>46295</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65406,7 +65406,7 @@
         <v>46261</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65479,7 +65479,7 @@
         <v>46181</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65557,7 +65557,7 @@
         <v>46034</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>44665</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65703,7 +65703,7 @@
         <v>44592</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65776,7 +65776,7 @@
         <v>44587</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65849,7 +65849,7 @@
         <v>44594</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65922,7 +65922,7 @@
         <v>44693</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65995,7 +65995,7 @@
         <v>44587</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66068,7 +66068,7 @@
         <v>44973</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66141,7 +66141,7 @@
         <v>45422</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66214,7 +66214,7 @@
         <v>45649</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66287,7 +66287,7 @@
         <v>45457</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66360,7 +66360,7 @@
         <v>45088</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66433,7 +66433,7 @@
         <v>45469</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66506,7 +66506,7 @@
         <v>45000</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66579,7 +66579,7 @@
         <v>45224</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66652,7 +66652,7 @@
         <v>45572</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66725,7 +66725,7 @@
         <v>45056</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66798,7 +66798,7 @@
         <v>45558</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66871,7 +66871,7 @@
         <v>44806</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66944,7 +66944,7 @@
         <v>45649</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67017,7 +67017,7 @@
         <v>45056</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67090,7 +67090,7 @@
         <v>45649</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67163,7 +67163,7 @@
         <v>45357</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67236,7 +67236,7 @@
         <v>45088</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67309,7 +67309,7 @@
         <v>45335</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67382,7 +67382,7 @@
         <v>45231</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67455,7 +67455,7 @@
         <v>45572</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67528,7 +67528,7 @@
         <v>45056</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67601,7 +67601,7 @@
         <v>45750</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67674,7 +67674,7 @@
         <v>45847</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67747,7 +67747,7 @@
         <v>45923</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67820,7 +67820,7 @@
         <v>45919</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67893,7 +67893,7 @@
         <v>45926</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67966,7 +67966,7 @@
         <v>45982</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68039,7 +68039,7 @@
         <v>45982</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68112,7 +68112,7 @@
         <v>46030</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68185,7 +68185,7 @@
         <v>46244</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68258,7 +68258,7 @@
         <v>46295</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -601,7 +601,7 @@
         <v>46153</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>43929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>46153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45568</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45889</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45730</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45358</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44606</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>44839</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>44504</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>45561</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>44867</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>46153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>46153</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>46211</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>45643</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45189</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>45999</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46153</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>46164</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>46174</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>46210</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46247</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44628</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>45056</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44490</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45695</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>45316</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45352</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45042</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>45652</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>44656</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45888</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>46126</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>46058</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>44853</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44748</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>44593</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>45188</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>45174</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>45446</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45447</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45888</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>45104</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45075</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45110</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>45818</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44785</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45093</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45850</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>45154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44869</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>46009</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>45604</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44917</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>45222</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>46141</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44595</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44853</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>45335</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44860</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45813</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44612</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>44602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>44951</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45649</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45215</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44882</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>45279</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45096</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45155</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>45898</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>45545</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>44908</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>45594</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>45541</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44909</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>45547</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>45701</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>45118</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>45758</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>45449</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44648</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>45581</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>45616</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>45307</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>45730</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>46094</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>46109</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44917</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>46002</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>46002</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>44798</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45069</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>45111</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44966</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>46057</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>46141</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>46153</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>46153</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>46153</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>46169</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>46183</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>46190</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>46153</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>46254</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>46300</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>46302</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45940</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>46230</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>44592</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>44603</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>44590</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>44830</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45572</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>46293</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>44491</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>44630</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>44889</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44691</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>44859</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44861</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44581</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44844</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44816</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44571</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44645</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44565</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>44831</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>44783</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44566</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44684</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44493</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44806</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>44488</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>44833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>44587</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>44624</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>44805</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44593</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>44617</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>44526</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44593</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44578</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>44551</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>44508</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>44813</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44776</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>44870</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44851</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>44785</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44771</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>44634</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>44634</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>44657</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44650</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44629</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44494</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44727</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>44839</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44881</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>44796</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44551</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>44866</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>44866</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>44612</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44755</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45763</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44867</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>44551</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45075</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45253</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>44870</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45078</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45342</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44587</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>44827</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45488</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45050</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>45401</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45149</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45075</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45336</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45679</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>44880</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44874</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45013</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45090</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>45091</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45078</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45093</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>45606</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45190</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>44882</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>44586</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45093</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45216</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45341</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45210</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45296</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45162</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44825</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>45342</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45096</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>44865</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44909</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>45103</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>45043</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45054</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>45085</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44890</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45575</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>45308</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45649</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45649</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45240</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45103</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45103</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45156</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45313</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44785</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45376</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45761</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45440</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>44868</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45394</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45011</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45210</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>45368</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45110</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45369</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>45149</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45591</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45635</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45469</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45028</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45478</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45510</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44811</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>44867</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>45359</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45429</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45118</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45121</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45280</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45123</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>44839</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>44594</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45331</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45117</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45791</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>45737</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45022</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45084</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>45253</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>44778</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45056</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45149</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45561</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45561</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44489</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45205</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45849</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45253</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>44973</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44973</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45685</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>45103</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45791</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>44505</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45883</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45883</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45698</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>45603</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>45240</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>45603</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>45603</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>44982</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45233</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44957</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44957</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>44903</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45849</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45477</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45079</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45882</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>45169</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45107</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45407</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44953</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>44936</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>44882</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45156</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44609</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45888</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45628</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>45069</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>45166</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45163</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>45342</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>45373</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>44528</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45369</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>45356</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>45321</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>45429</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>45894</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28299,7 +28299,7 @@
         <v>45894</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>45013</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>45560</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>45341</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28591,7 +28591,7 @@
         <v>45798</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         <v>45475</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45475</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45852</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45096</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45679</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45729</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44938</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>45714</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>44915</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45649</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45649</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45649</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>44973</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45217</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45908</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45762</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>44972</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>44999</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45666</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45840</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45181</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>45089</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45070</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>44606</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45551</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44488</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45601</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45449</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45545</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45744</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45476</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45260</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45489</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>44914</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>45547</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45616</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>45544</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45096</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45474</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>45169</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44580</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45587</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45079</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>45665</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>45706</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>45320</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44904</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45572</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45917</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>45442</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45230</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>44959</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>45370</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>45246</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>45357</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>45113</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>45367</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45673</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>45664</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>45301</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>45625</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45489</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>44928</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45785</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45131</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>44544</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>45763</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>44959</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>45786</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45315</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45401</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45016</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45923</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>45534</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>45561</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>44692</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45561</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45561</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>44566</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45103</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45092</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>45408</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>45197</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>45926</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>44992</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45098</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>44873</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>45035</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>45701</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>45145</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45145</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44593</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44832</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45761</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>45218</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>45335</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45338</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45222</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>44973</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45560</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45385</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>44645</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>44910</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45372</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>45037</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44939</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>45223</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45230</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>45367</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45664</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>44697</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>44677</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>45373</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44733</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>44867</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45063</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44970</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45082</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45525</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>45191</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>45191</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44657</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>44594</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>45049</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>44622</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45938</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45095</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>45695</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45637</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>44713</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>45812</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>45415</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45071</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>45072</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45586</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>45439</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>45740</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>45945</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>44825</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>45070</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45367</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45762</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39080,7 +39080,7 @@
         <v>45411</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45118</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45392</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45196</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>45946</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>44713</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>45121</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>45121</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>44746</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>44833</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45818</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>45946</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>44690</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44798</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>45824</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>45307</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45359</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>45821</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>45824</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>44684</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>45089</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>45629</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>44931</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>45182</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40847,7 +40847,7 @@
         <v>45825</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45175</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>45106</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45093</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45244</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41212,7 +41212,7 @@
         <v>45741</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>45057</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>45057</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>45756</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>45958</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41577,7 +41577,7 @@
         <v>45958</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>45958</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45958</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41796,7 +41796,7 @@
         <v>45834</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>45834</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>45834</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>45211</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>44819</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>45833</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45187</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>45834</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42380,7 +42380,7 @@
         <v>45407</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42453,7 +42453,7 @@
         <v>45681</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45239</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>45837</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45837</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>44742</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44909</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42896,7 +42896,7 @@
         <v>45175</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45198</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45210</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
         <v>45475</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>45211</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44749</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>44999</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>44721</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43480,7 +43480,7 @@
         <v>45616</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>44743</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45846</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>45817</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45175</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45846</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45616</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>45414</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>45756</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>44909</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45706</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>45119</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45244</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>45852</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>44841</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45975</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45484</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>45409</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45694</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45775</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>44803</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>44693</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>45856</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>45448</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>45856</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>44739</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>44746</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>45022</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45254</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45818</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45616</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>45330</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>44497</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>44974</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45111</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>45366</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45980</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45231</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45217</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>45980</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>44917</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45980</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46581,7 +46581,7 @@
         <v>44959</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45273</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>44819</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45301</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>45301</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45763</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>44818</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45880</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>45327</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45369</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45762</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>44945</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>44494</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>45733</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47613,7 +47613,7 @@
         <v>45880</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45092</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>45881</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>44991</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45882</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47988,7 +47988,7 @@
         <v>45554</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45346</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>45728</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>44816</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48290,7 +48290,7 @@
         <v>45278</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48363,7 +48363,7 @@
         <v>44881</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>44844</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         <v>45090</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45610</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>44756</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48733,7 +48733,7 @@
         <v>45091</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>45986</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48879,7 +48879,7 @@
         <v>45509</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>44868</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45189</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49103,7 +49103,7 @@
         <v>45985</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>44621</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45728</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45986</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
         <v>45484</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>44865</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49546,7 +49546,7 @@
         <v>46104</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>44700</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>45072</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>46106</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>44985</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>44889</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45135</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>46106</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50140,7 +50140,7 @@
         <v>45463</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50213,7 +50213,7 @@
         <v>45055</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>45534</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45111</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45987</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>45761</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>46113</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>46112</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45426</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45394</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50880,7 +50880,7 @@
         <v>45090</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50953,7 +50953,7 @@
         <v>45342</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51026,7 +51026,7 @@
         <v>46112</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51099,7 +51099,7 @@
         <v>46112</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>45400</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51245,7 +51245,7 @@
         <v>45552</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51318,7 +51318,7 @@
         <v>44909</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>44973</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>46122</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51537,7 +51537,7 @@
         <v>46125</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>46127</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45999</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51756,7 +51756,7 @@
         <v>46000</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51829,7 +51829,7 @@
         <v>46127</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51902,7 +51902,7 @@
         <v>44904</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45174</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45335</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52126,7 +52126,7 @@
         <v>44992</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52199,7 +52199,7 @@
         <v>46133</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52272,7 +52272,7 @@
         <v>44579</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>46134</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>46134</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52491,7 +52491,7 @@
         <v>46134</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52564,7 +52564,7 @@
         <v>44928</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52637,7 +52637,7 @@
         <v>44594</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52710,7 +52710,7 @@
         <v>44933</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>44977</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52856,7 +52856,7 @@
         <v>46133</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52929,7 +52929,7 @@
         <v>44881</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>45478</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53075,7 +53075,7 @@
         <v>45966</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45188</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53221,7 +53221,7 @@
         <v>45363</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45914</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53367,7 +53367,7 @@
         <v>45930</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53445,7 +53445,7 @@
         <v>45244</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53518,7 +53518,7 @@
         <v>45820</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45841</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53669,7 +53669,7 @@
         <v>45072</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53742,7 +53742,7 @@
         <v>45966</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53815,7 +53815,7 @@
         <v>45705</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>45951</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53961,7 +53961,7 @@
         <v>45371</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54034,7 +54034,7 @@
         <v>45478</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54107,7 +54107,7 @@
         <v>44914</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>45577</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54253,7 +54253,7 @@
         <v>45980</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54331,7 +54331,7 @@
         <v>44497</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54404,7 +54404,7 @@
         <v>44949</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54477,7 +54477,7 @@
         <v>45931</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45512</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>45392</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54701,7 +54701,7 @@
         <v>45859</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>45260</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54847,7 +54847,7 @@
         <v>45975</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>45188</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45644</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>45551</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         <v>45931</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>45098</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55290,7 +55290,7 @@
         <v>45862</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>44909</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>45713</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>45385</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>45056</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>45606</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55728,7 +55728,7 @@
         <v>45887</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55801,7 +55801,7 @@
         <v>45075</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55874,7 +55874,7 @@
         <v>45327</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55947,7 +55947,7 @@
         <v>46000</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>46052</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>44900</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56166,7 +56166,7 @@
         <v>45213</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56239,7 +56239,7 @@
         <v>44904</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56312,7 +56312,7 @@
         <v>46029</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56385,7 +56385,7 @@
         <v>44909</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>45077</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56531,7 +56531,7 @@
         <v>45091</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45946</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>44494</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56750,7 +56750,7 @@
         <v>45063</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56823,7 +56823,7 @@
         <v>44798</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56896,7 +56896,7 @@
         <v>44853</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45470</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>45021</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45079</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>45534</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57261,7 +57261,7 @@
         <v>45572</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45668</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>46139</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57480,7 +57480,7 @@
         <v>45832</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>44713</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>46078</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57699,7 +57699,7 @@
         <v>44908</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>44974</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57845,7 +57845,7 @@
         <v>45079</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57918,7 +57918,7 @@
         <v>45208</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57991,7 +57991,7 @@
         <v>45525</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58064,7 +58064,7 @@
         <v>46058</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58137,7 +58137,7 @@
         <v>45590</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58210,7 +58210,7 @@
         <v>45175</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>44973</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58356,7 +58356,7 @@
         <v>46141</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>46051</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58512,7 +58512,7 @@
         <v>46141</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58590,7 +58590,7 @@
         <v>45392</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58663,7 +58663,7 @@
         <v>46141</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>46064</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>46064</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58887,7 +58887,7 @@
         <v>46069</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58960,7 +58960,7 @@
         <v>46067</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59033,7 +59033,7 @@
         <v>46069</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59106,7 +59106,7 @@
         <v>46153</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59184,7 +59184,7 @@
         <v>46072</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59257,7 +59257,7 @@
         <v>46072</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59330,7 +59330,7 @@
         <v>46153</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59408,7 +59408,7 @@
         <v>46078</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59481,7 +59481,7 @@
         <v>46083</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59554,7 +59554,7 @@
         <v>46083</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>46155</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59700,7 +59700,7 @@
         <v>46087</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45894</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59846,7 +59846,7 @@
         <v>46086</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>46160</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59992,7 +59992,7 @@
         <v>46057</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60065,7 +60065,7 @@
         <v>46092</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60138,7 +60138,7 @@
         <v>46092</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60211,7 +60211,7 @@
         <v>46168</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45670</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>46175</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>46169</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         <v>46177</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>46178</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60659,7 +60659,7 @@
         <v>46178</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60732,7 +60732,7 @@
         <v>46184</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60805,7 +60805,7 @@
         <v>46184</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60878,7 +60878,7 @@
         <v>46182</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>46190</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61029,7 +61029,7 @@
         <v>46197</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61107,7 +61107,7 @@
         <v>46197</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>46197</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         <v>46199</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61336,7 +61336,7 @@
         <v>46205</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61409,7 +61409,7 @@
         <v>46269</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61482,7 +61482,7 @@
         <v>46272</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>46269</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61628,7 +61628,7 @@
         <v>46273</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61701,7 +61701,7 @@
         <v>46274</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>46275</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61852,7 +61852,7 @@
         <v>46279</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>46279</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>46282</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         <v>46238</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62149,7 +62149,7 @@
         <v>46238</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62227,7 +62227,7 @@
         <v>46283</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62300,7 +62300,7 @@
         <v>46175</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62373,7 +62373,7 @@
         <v>46241</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62446,7 +62446,7 @@
         <v>45744</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62519,7 +62519,7 @@
         <v>46286</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62592,7 +62592,7 @@
         <v>46134</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62665,7 +62665,7 @@
         <v>46246</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62738,7 +62738,7 @@
         <v>46246</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>45792</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62889,7 +62889,7 @@
         <v>45938</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62962,7 +62962,7 @@
         <v>46289</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63035,7 +63035,7 @@
         <v>44594</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63108,7 +63108,7 @@
         <v>46250</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63181,7 +63181,7 @@
         <v>46248</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>46253</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63332,7 +63332,7 @@
         <v>46295</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63405,7 +63405,7 @@
         <v>46253</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63483,7 +63483,7 @@
         <v>46254</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63561,7 +63561,7 @@
         <v>46300</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63639,7 +63639,7 @@
         <v>46246</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63712,7 +63712,7 @@
         <v>46255</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63790,7 +63790,7 @@
         <v>46112</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>46029</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63936,7 +63936,7 @@
         <v>46255</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>46300</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>46300</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64155,7 +64155,7 @@
         <v>46300</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64228,7 +64228,7 @@
         <v>46300</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64306,7 +64306,7 @@
         <v>46300</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         <v>46297</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64457,7 +64457,7 @@
         <v>46300</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64530,7 +64530,7 @@
         <v>46300</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64603,7 +64603,7 @@
         <v>45940</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64676,7 +64676,7 @@
         <v>46252</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64749,7 +64749,7 @@
         <v>46198</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64822,7 +64822,7 @@
         <v>46302</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64895,7 +64895,7 @@
         <v>46301</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64968,7 +64968,7 @@
         <v>46190</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65041,7 +65041,7 @@
         <v>46301</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65114,7 +65114,7 @@
         <v>46301</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65187,7 +65187,7 @@
         <v>46303</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65260,7 +65260,7 @@
         <v>46295</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65333,7 +65333,7 @@
         <v>46295</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65406,7 +65406,7 @@
         <v>46261</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65479,7 +65479,7 @@
         <v>46181</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65557,7 +65557,7 @@
         <v>46034</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>44665</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65703,7 +65703,7 @@
         <v>44592</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65776,7 +65776,7 @@
         <v>44587</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65849,7 +65849,7 @@
         <v>44594</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65922,7 +65922,7 @@
         <v>44693</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65995,7 +65995,7 @@
         <v>44587</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66068,7 +66068,7 @@
         <v>44973</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66141,7 +66141,7 @@
         <v>45422</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66214,7 +66214,7 @@
         <v>45649</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66287,7 +66287,7 @@
         <v>45457</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66360,7 +66360,7 @@
         <v>45088</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66433,7 +66433,7 @@
         <v>45469</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66506,7 +66506,7 @@
         <v>45000</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66579,7 +66579,7 @@
         <v>45224</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66652,7 +66652,7 @@
         <v>45572</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66725,7 +66725,7 @@
         <v>45056</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66798,7 +66798,7 @@
         <v>45558</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66871,7 +66871,7 @@
         <v>44806</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66944,7 +66944,7 @@
         <v>45649</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67017,7 +67017,7 @@
         <v>45056</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67090,7 +67090,7 @@
         <v>45649</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67163,7 +67163,7 @@
         <v>45357</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67236,7 +67236,7 @@
         <v>45088</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67309,7 +67309,7 @@
         <v>45335</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67382,7 +67382,7 @@
         <v>45231</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67455,7 +67455,7 @@
         <v>45572</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67528,7 +67528,7 @@
         <v>45056</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67601,7 +67601,7 @@
         <v>45750</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67674,7 +67674,7 @@
         <v>45847</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67747,7 +67747,7 @@
         <v>45923</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67820,7 +67820,7 @@
         <v>45919</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67893,7 +67893,7 @@
         <v>45926</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67966,7 +67966,7 @@
         <v>45982</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68039,7 +68039,7 @@
         <v>45982</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68112,7 +68112,7 @@
         <v>46030</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68185,7 +68185,7 @@
         <v>46244</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68258,7 +68258,7 @@
         <v>46295</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -601,7 +601,7 @@
         <v>46153</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>43929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>46153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45568</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45889</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45730</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45358</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44606</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>44839</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>46153</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44504</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>45561</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>46153</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>46153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>44867</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>45643</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44587</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>46153</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>46164</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45189</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>45999</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>46174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>46210</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45093</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>46247</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>44628</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>45056</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44490</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>45352</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>45695</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>45652</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>45042</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45316</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>45888</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>46126</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44656</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>46058</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>44748</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>44853</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>44593</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45110</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45222</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>45446</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44785</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>45604</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45888</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>46141</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>45075</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>46009</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44869</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>45154</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>44917</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45174</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>45104</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44980</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>45093</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>45447</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45818</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45850</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>44853</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>45335</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44595</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>44607</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>44860</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>45813</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>46308</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>44612</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>45594</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>44966</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45111</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44917</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>44951</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>45279</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>45096</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45898</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>46141</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>46153</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>46153</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>46153</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45649</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45758</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>46169</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>46002</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>46002</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45069</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>45449</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>46057</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>46183</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>44648</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>44882</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>46190</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44908</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45155</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>46094</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>45215</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>46109</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45545</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>45581</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>45118</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>44798</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45730</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>46153</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>45307</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>46254</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>46300</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>45541</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45701</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>46302</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>44909</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>45547</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45940</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>46230</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45616</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44592</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>44830</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45572</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44603</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>44590</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>46293</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>44491</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>44630</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>44889</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44859</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44861</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>44691</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44581</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>44844</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>44816</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>44571</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>44645</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>44565</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>44831</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>44783</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>44566</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44684</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>44806</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>44493</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>44488</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>44833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>44587</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44624</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44776</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44870</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44771</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>44657</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44612</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44617</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>44551</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>44508</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44851</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44494</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>44629</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>44881</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>44796</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>44551</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>44593</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>44813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44785</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44650</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>44839</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>44805</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>44593</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>44526</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>44578</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44634</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44634</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44727</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>44551</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>44870</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>44587</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>45273</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>45341</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45775</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>45103</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45649</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>45649</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45022</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45488</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>44489</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45123</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45230</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45054</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45162</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45075</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45092</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>44657</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45091</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>44819</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45181</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45606</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>44544</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44973</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>45278</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>44818</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>44933</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44985</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44692</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>45307</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45394</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45175</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45763</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45028</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45376</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45037</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45327</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45021</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45728</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>44909</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>44909</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44973</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45118</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>44594</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>44494</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45448</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>45107</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45729</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45149</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>45189</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>45260</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>44833</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45075</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45106</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45547</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45761</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45049</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45222</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>44882</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45121</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45366</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45346</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>44992</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45260</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>44778</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44690</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>44928</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45664</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45407</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>44867</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>44959</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45338</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45409</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45484</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44949</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>44959</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45063</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45254</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45188</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44915</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45394</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>44903</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45368</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45369</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45525</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>44721</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>44890</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>44853</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45331</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45561</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45429</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45561</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44497</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45223</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45210</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>45091</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>44914</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>44914</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44931</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45096</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45359</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>45240</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>45363</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45077</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>44936</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>45931</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45849</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>46058</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45946</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45572</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>45737</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44832</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45791</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45849</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44733</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45966</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45103</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45694</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45975</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>46052</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45713</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45253</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45603</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45685</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45191</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45577</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>44609</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>44865</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45478</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44505</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45791</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>45698</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45217</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45253</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45603</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45888</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45859</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45145</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45145</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>45914</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45930</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45628</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45163</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45169</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45182</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45166</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44819</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45894</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45894</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>44867</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>44528</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>45603</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45091</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45951</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45169</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>44982</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45233</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45862</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45798</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45966</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45103</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45103</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45820</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45841</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45832</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45887</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>46141</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>45534</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45327</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>46141</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>46141</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>45392</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45342</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>45852</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45321</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45649</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>45213</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>44868</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>45908</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>45629</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>45135</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45840</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         <v>44945</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>45211</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31505,7 +31505,7 @@
         <v>45762</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>45917</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>45637</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44811</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>45096</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45216</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44909</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44991</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>45069</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>45679</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44973</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45923</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>44684</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>44974</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45057</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>45057</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>44972</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>45926</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>45606</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>46153</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>45938</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>46153</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33126,7 +33126,7 @@
         <v>45217</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>45174</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>45385</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>45011</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44645</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45945</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45400</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>45231</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>45610</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>45055</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45946</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45744</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>45714</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>45946</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>45664</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>45253</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45411</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>45191</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>46155</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34518,7 +34518,7 @@
         <v>45474</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>45649</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45649</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>45958</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45762</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>44917</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>45958</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>45958</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>44938</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>45958</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>45560</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>46057</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>45894</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>44867</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>45280</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>44580</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45591</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>46160</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>45043</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45616</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45426</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45050</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>45330</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>45103</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>44974</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44693</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>44739</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45975</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>44494</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45296</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>45980</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45187</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>44586</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>44904</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>45980</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>45980</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>44798</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45985</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45733</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45415</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>44977</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>45035</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>44909</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>45986</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45090</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>45986</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>44621</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>45987</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>44579</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45372</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>44803</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>44904</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>44904</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>45560</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45079</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45763</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>45197</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>45469</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>46168</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45478</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>44939</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45999</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>46000</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>45313</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>45079</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45090</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45756</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45342</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44908</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>45561</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45670</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45090</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45110</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45078</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>45013</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45098</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>44900</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>45072</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45407</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>46000</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>44970</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>45763</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>45477</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>46029</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>45551</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>44868</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45728</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>44866</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45196</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>46175</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>46169</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>46178</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>46177</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>45190</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>45408</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>46178</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>45369</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>44957</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>44957</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         <v>45695</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41873,7 +41873,7 @@
         <v>45013</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41946,7 +41946,7 @@
         <v>45552</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>46051</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>45149</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>45440</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>45082</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42321,7 +42321,7 @@
         <v>44973</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>45092</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>46182</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>46184</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>44999</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>44841</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>45121</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>45575</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>46184</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>46064</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>46064</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45072</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>45022</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45470</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>46069</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>44959</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>46069</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>46067</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>46072</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>46072</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43791,7 +43791,7 @@
         <v>44839</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>45369</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>46078</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44010,7 +44010,7 @@
         <v>45093</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45463</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>45093</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>45121</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44302,7 +44302,7 @@
         <v>45561</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45561</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>44746</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44531,7 +44531,7 @@
         <v>45439</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>46083</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>46083</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45075</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>46086</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>46190</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45070</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>45244</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>44881</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45188,7 +45188,7 @@
         <v>46087</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>45740</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>44873</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>46092</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45480,7 +45480,7 @@
         <v>46092</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45084</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45626,7 +45626,7 @@
         <v>44973</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>45442</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45772,7 +45772,7 @@
         <v>45336</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>44844</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45918,7 +45918,7 @@
         <v>45079</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45991,7 +45991,7 @@
         <v>45315</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45341</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45509</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>45510</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>44713</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>46104</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46429,7 +46429,7 @@
         <v>45367</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45635</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45475</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>45475</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>46106</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46799,7 +46799,7 @@
         <v>46106</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>44825</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>45666</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>44497</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45554</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>46112</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>46197</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>46197</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47403,7 +47403,7 @@
         <v>46197</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>46112</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>46112</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47627,7 +47627,7 @@
         <v>45071</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>46113</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47773,7 +47773,7 @@
         <v>45117</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45356</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45175</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>44953</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>45335</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45335</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48216,7 +48216,7 @@
         <v>46122</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>45218</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45093</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>45078</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>44816</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>44928</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>46125</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46127</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>45414</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>44713</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>46127</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>46199</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>46133</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45385</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>46133</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49311,7 +49311,7 @@
         <v>45392</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>46134</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
         <v>46134</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>46134</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>44889</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45705</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>45111</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45131</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49895,7 +49895,7 @@
         <v>44756</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45063</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>44874</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50119,7 +50119,7 @@
         <v>46078</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50192,7 +50192,7 @@
         <v>45980</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50270,7 +50270,7 @@
         <v>45478</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>46139</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45119</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45644</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>45551</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>44677</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>45931</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45198</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>45301</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>45301</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51005,7 +51005,7 @@
         <v>45512</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>46205</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>44742</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45359</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>44713</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45096</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>45590</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>44798</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>44593</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45098</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>45392</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>44746</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45056</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45118</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>45056</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>45544</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>44827</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>45016</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>44825</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>46272</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>46273</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45095</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>46274</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45244</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>46275</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45211</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45367</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>46279</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45072</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45244</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>46279</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>44999</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45188</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>46238</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>45342</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53570,7 +53570,7 @@
         <v>44910</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45156</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53716,7 +53716,7 @@
         <v>46238</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>44566</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53867,7 +53867,7 @@
         <v>45373</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>45210</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54013,7 +54013,7 @@
         <v>44909</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54086,7 +54086,7 @@
         <v>44909</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54159,7 +54159,7 @@
         <v>45668</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>46282</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>46283</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>45156</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>44866</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54524,7 +54524,7 @@
         <v>44755</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>44594</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>44992</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45373</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45085</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>46175</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45475</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>45205</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>46286</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>46241</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>45401</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45744</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45239</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>45089</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>45079</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45429</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>46246</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55770,7 +55770,7 @@
         <v>45762</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55843,7 +55843,7 @@
         <v>44785</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55916,7 +55916,7 @@
         <v>45113</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55989,7 +55989,7 @@
         <v>44880</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>46246</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56135,7 +56135,7 @@
         <v>44488</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45089</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45208</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>46289</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56427,7 +56427,7 @@
         <v>45534</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56500,7 +56500,7 @@
         <v>45342</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>46134</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         <v>45484</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>44594</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56792,7 +56792,7 @@
         <v>45706</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56865,7 +56865,7 @@
         <v>46250</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56938,7 +56938,7 @@
         <v>46248</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57011,7 +57011,7 @@
         <v>45756</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57084,7 +57084,7 @@
         <v>44700</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>44622</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45240</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57303,7 +57303,7 @@
         <v>45938</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57376,7 +57376,7 @@
         <v>45792</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57454,7 +57454,7 @@
         <v>44865</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>45761</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57605,7 +57605,7 @@
         <v>44749</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>44973</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>45175</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45308</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57897,7 +57897,7 @@
         <v>45149</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>45210</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58043,7 +58043,7 @@
         <v>44881</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58116,7 +58116,7 @@
         <v>46295</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45175</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58262,7 +58262,7 @@
         <v>45371</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>44743</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>44594</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58481,7 +58481,7 @@
         <v>45320</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58554,7 +58554,7 @@
         <v>46112</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45741</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45681</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58778,7 +58778,7 @@
         <v>46255</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>44882</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58929,7 +58929,7 @@
         <v>46253</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59007,7 +59007,7 @@
         <v>46246</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59080,7 +59080,7 @@
         <v>45940</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59153,7 +59153,7 @@
         <v>46252</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59226,7 +59226,7 @@
         <v>46254</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59304,7 +59304,7 @@
         <v>46297</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59377,7 +59377,7 @@
         <v>46029</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59450,7 +59450,7 @@
         <v>46253</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59528,7 +59528,7 @@
         <v>45679</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59601,7 +59601,7 @@
         <v>46300</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59674,7 +59674,7 @@
         <v>45586</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59747,7 +59747,7 @@
         <v>46255</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59820,7 +59820,7 @@
         <v>46300</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59893,7 +59893,7 @@
         <v>46300</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>44606</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60044,7 +60044,7 @@
         <v>46300</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60117,7 +60117,7 @@
         <v>45545</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60190,7 +60190,7 @@
         <v>45449</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60263,7 +60263,7 @@
         <v>46300</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>46300</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>45070</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>45601</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45476</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60638,7 +60638,7 @@
         <v>45489</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60711,7 +60711,7 @@
         <v>46198</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60784,7 +60784,7 @@
         <v>46301</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60857,7 +60857,7 @@
         <v>45587</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60930,7 +60930,7 @@
         <v>46190</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>46300</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61076,7 +61076,7 @@
         <v>45785</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>45230</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61222,7 +61222,7 @@
         <v>46300</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61295,7 +61295,7 @@
         <v>45489</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61368,7 +61368,7 @@
         <v>45625</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61441,7 +61441,7 @@
         <v>45706</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61514,7 +61514,7 @@
         <v>45786</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61587,7 +61587,7 @@
         <v>45673</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61660,7 +61660,7 @@
         <v>45572</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61733,7 +61733,7 @@
         <v>45665</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61806,7 +61806,7 @@
         <v>45534</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61879,7 +61879,7 @@
         <v>45357</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61952,7 +61952,7 @@
         <v>45301</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62025,7 +62025,7 @@
         <v>45401</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62098,7 +62098,7 @@
         <v>46295</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62171,7 +62171,7 @@
         <v>45367</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62244,7 +62244,7 @@
         <v>46301</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62317,7 +62317,7 @@
         <v>45246</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>45370</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62463,7 +62463,7 @@
         <v>46295</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62536,7 +62536,7 @@
         <v>46301</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>46303</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62682,7 +62682,7 @@
         <v>46302</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62755,7 +62755,7 @@
         <v>46261</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>45701</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62901,7 +62901,7 @@
         <v>45761</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62974,7 +62974,7 @@
         <v>46034</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63047,7 +63047,7 @@
         <v>44697</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63120,7 +63120,7 @@
         <v>46181</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63198,7 +63198,7 @@
         <v>46307</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63271,7 +63271,7 @@
         <v>45525</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>45812</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63417,7 +63417,7 @@
         <v>45818</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63490,7 +63490,7 @@
         <v>45821</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>45825</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63636,7 +63636,7 @@
         <v>45824</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63714,7 +63714,7 @@
         <v>46269</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>46269</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63860,7 +63860,7 @@
         <v>45824</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63933,7 +63933,7 @@
         <v>45833</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45834</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64079,7 +64079,7 @@
         <v>45834</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64152,7 +64152,7 @@
         <v>45834</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64225,7 +64225,7 @@
         <v>45834</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64298,7 +64298,7 @@
         <v>45837</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64371,7 +64371,7 @@
         <v>45837</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64444,7 +64444,7 @@
         <v>45616</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64517,7 +64517,7 @@
         <v>45616</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64590,7 +64590,7 @@
         <v>45817</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>45846</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64736,7 +64736,7 @@
         <v>45846</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64809,7 +64809,7 @@
         <v>45852</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64882,7 +64882,7 @@
         <v>45856</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64960,7 +64960,7 @@
         <v>45856</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65038,7 +65038,7 @@
         <v>45818</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65111,7 +65111,7 @@
         <v>45616</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65184,7 +65184,7 @@
         <v>45881</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65262,7 +65262,7 @@
         <v>45880</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65335,7 +65335,7 @@
         <v>45880</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65408,7 +65408,7 @@
         <v>45882</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65481,7 +65481,7 @@
         <v>45882</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65554,7 +65554,7 @@
         <v>45883</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65627,7 +65627,7 @@
         <v>45883</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65700,7 +65700,7 @@
         <v>44665</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65773,7 +65773,7 @@
         <v>44973</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65846,7 +65846,7 @@
         <v>45422</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65919,7 +65919,7 @@
         <v>45649</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65992,7 +65992,7 @@
         <v>45457</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66065,7 +66065,7 @@
         <v>45088</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66138,7 +66138,7 @@
         <v>45469</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66211,7 +66211,7 @@
         <v>45000</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66284,7 +66284,7 @@
         <v>45224</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66357,7 +66357,7 @@
         <v>45572</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66430,7 +66430,7 @@
         <v>45056</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66503,7 +66503,7 @@
         <v>44592</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66576,7 +66576,7 @@
         <v>45558</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66649,7 +66649,7 @@
         <v>44587</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66722,7 +66722,7 @@
         <v>44806</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66795,7 +66795,7 @@
         <v>45649</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66868,7 +66868,7 @@
         <v>45056</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66941,7 +66941,7 @@
         <v>45649</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67014,7 +67014,7 @@
         <v>44594</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67087,7 +67087,7 @@
         <v>44693</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67160,7 +67160,7 @@
         <v>45357</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67233,7 +67233,7 @@
         <v>45088</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67306,7 +67306,7 @@
         <v>45335</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67379,7 +67379,7 @@
         <v>45231</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67452,7 +67452,7 @@
         <v>44587</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67525,7 +67525,7 @@
         <v>45572</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67598,7 +67598,7 @@
         <v>45056</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67671,7 +67671,7 @@
         <v>45750</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67744,7 +67744,7 @@
         <v>45847</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67817,7 +67817,7 @@
         <v>45923</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67890,7 +67890,7 @@
         <v>45919</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67963,7 +67963,7 @@
         <v>45926</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>45982</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68109,7 +68109,7 @@
         <v>45982</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68182,7 +68182,7 @@
         <v>46030</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68255,7 +68255,7 @@
         <v>46244</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68328,7 +68328,7 @@
         <v>46295</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68401,7 +68401,7 @@
         <v>46308</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -601,7 +601,7 @@
         <v>46153</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45006</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>43929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>45099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>46153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45568</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45889</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45730</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>45358</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44606</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>44839</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>46153</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44504</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>45561</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>46153</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>46153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>44867</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>45643</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>44587</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>46153</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>46164</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45189</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>45999</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>46174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>46210</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45093</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>46247</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>44628</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>45056</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44490</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>45352</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>45695</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>45652</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>45042</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45316</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>45888</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>46126</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44656</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>46058</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>44748</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>44853</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>44593</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45110</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45222</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>45446</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44785</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>45604</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45888</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>46141</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>45075</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>46009</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44869</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>45154</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>44917</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45174</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>45104</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44980</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>45093</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>45447</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45818</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45850</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>44853</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>45335</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44595</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>44607</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>44860</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>45813</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>46308</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>44612</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>45594</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>44966</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45111</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44917</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>44951</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>45279</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>45096</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45898</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>46141</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>46153</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>46153</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>46153</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45649</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45758</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>46169</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>46002</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>46002</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45069</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>45449</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>46057</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>46183</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>44648</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>44882</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>46190</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44908</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45155</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>46094</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>45215</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>46109</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45545</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>45581</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>45118</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>44798</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45730</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>46153</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>45307</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>46254</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>46300</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>45541</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45701</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>46302</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>44909</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>45547</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45940</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>46230</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45616</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44592</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>44830</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45572</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44603</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>44590</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>46293</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>44491</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>44630</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>44889</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44859</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44861</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>44691</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44581</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>44844</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>44816</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>44571</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>44645</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>44565</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>44831</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>44783</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>44566</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44684</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>44806</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>44493</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>44488</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>44833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>44587</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44624</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44776</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44870</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44771</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>44657</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44612</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44617</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>44551</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>44508</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44851</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44494</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>44629</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>44881</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>44796</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>44551</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>44593</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>44813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44785</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44650</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>44839</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>44805</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>44593</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>44526</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>44578</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44634</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44634</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44727</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>44551</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>44870</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>44587</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>45273</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>45341</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45775</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>45103</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45649</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>45649</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45022</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45488</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>44489</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45123</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45230</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45054</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45162</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45075</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45092</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>44657</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45091</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>44819</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45181</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45606</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>44544</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44973</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>45278</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>44818</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>44933</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44985</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44692</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>45307</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45394</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45175</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45763</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45028</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45376</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45037</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45327</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45021</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45728</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>44909</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>44909</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44973</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45118</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>44594</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>44494</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45448</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>45107</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45729</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45149</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>45189</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>45260</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>44833</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45075</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45106</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45547</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45761</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45049</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45222</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>44882</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45121</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45366</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45346</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>44992</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45260</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>44778</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44690</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>44928</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45664</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45407</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>44867</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>44959</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45338</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45409</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45484</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44949</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>44959</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45063</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45254</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45188</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44915</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45394</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>44903</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45368</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45369</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45525</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>44721</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>44890</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>44853</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45331</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45561</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45429</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45561</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44497</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45223</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45210</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>45091</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>44914</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>44914</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44931</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45096</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45359</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>45240</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>45363</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45077</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>44936</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>45931</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45849</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>46058</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45946</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45572</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>45737</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44832</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45791</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45849</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44733</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45966</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45103</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45694</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45975</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>46052</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45713</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45253</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45603</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45685</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45191</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45577</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>44609</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>44865</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45478</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44505</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45791</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>45698</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45217</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45253</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45603</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45888</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45859</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45145</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45145</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>45914</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45930</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45628</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45163</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45169</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45182</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45166</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44819</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45894</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45894</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>44867</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>44528</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>45603</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45091</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45951</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45169</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>44982</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45233</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45862</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45798</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45966</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45103</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45103</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45820</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45841</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45832</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45887</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>46141</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>45534</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45327</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>46141</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>46141</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>45392</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45342</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>45852</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45321</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45649</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>45213</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>44868</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>45908</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>45629</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>45135</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45840</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         <v>44945</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>45211</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31505,7 +31505,7 @@
         <v>45762</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>45917</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>45637</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44811</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>45096</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45216</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44909</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44991</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>45069</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>45679</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44973</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45923</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>44684</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>44974</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45057</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>45057</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>44972</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>45926</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>45606</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>46153</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>45938</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>46153</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33126,7 +33126,7 @@
         <v>45217</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>45174</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>45385</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>45011</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44645</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45945</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45400</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>45231</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>45610</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>45055</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45946</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45744</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>45714</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>45946</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>45664</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>45253</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45411</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>45191</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>46155</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34518,7 +34518,7 @@
         <v>45474</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>45649</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45649</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>45958</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45762</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>44917</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>45958</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>45958</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>44938</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>45958</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>45560</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>46057</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>45894</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>44867</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>45280</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>44580</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45591</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>46160</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>45043</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45616</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45426</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45050</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>45330</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>45103</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>44974</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44693</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>44739</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45975</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>44494</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45296</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>45980</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45187</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>44586</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>44904</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>45980</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>45980</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>44798</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45985</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45733</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45415</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>44977</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>45035</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>44909</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>45986</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45090</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>45986</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>44621</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>45987</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>44579</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45372</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>44803</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>44904</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>44904</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>45560</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45079</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45763</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>45197</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>45469</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>46168</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45478</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>44939</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45999</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>46000</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>45313</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>45079</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45090</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45756</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45342</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44908</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>45561</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45670</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45090</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45110</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45078</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>45013</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45098</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>44900</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>45072</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45407</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>46000</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>44970</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>45763</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>45477</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>46029</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>45551</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>44868</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45728</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>44866</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45196</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>46175</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>46169</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>46178</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>46177</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>45190</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>45408</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>46178</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>45369</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>44957</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>44957</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         <v>45695</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41873,7 +41873,7 @@
         <v>45013</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41946,7 +41946,7 @@
         <v>45552</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>46051</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>45149</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>45440</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>45082</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42321,7 +42321,7 @@
         <v>44973</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>45092</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>46182</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>46184</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>44999</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>44841</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>45121</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>45575</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>46184</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>46064</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>46064</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45072</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>45022</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45470</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>46069</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>44959</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>46069</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>46067</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>46072</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>46072</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43791,7 +43791,7 @@
         <v>44839</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>45369</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>46078</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44010,7 +44010,7 @@
         <v>45093</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45463</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>45093</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>45121</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44302,7 +44302,7 @@
         <v>45561</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45561</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>44746</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44531,7 +44531,7 @@
         <v>45439</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>46083</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>46083</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45075</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>46086</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>46190</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45070</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>45244</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>44881</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45188,7 +45188,7 @@
         <v>46087</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>45740</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>44873</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>46092</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45480,7 +45480,7 @@
         <v>46092</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45084</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45626,7 +45626,7 @@
         <v>44973</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>45442</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45772,7 +45772,7 @@
         <v>45336</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>44844</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45918,7 +45918,7 @@
         <v>45079</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45991,7 +45991,7 @@
         <v>45315</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45341</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45509</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>45510</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>44713</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>46104</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46429,7 +46429,7 @@
         <v>45367</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45635</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45475</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>45475</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>46106</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46799,7 +46799,7 @@
         <v>46106</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>44825</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>45666</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>44497</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45554</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>46112</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>46197</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>46197</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47403,7 +47403,7 @@
         <v>46197</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>46112</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>46112</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47627,7 +47627,7 @@
         <v>45071</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>46113</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47773,7 +47773,7 @@
         <v>45117</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45356</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45175</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>44953</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>45335</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45335</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48216,7 +48216,7 @@
         <v>46122</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>45218</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45093</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>45078</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>44816</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>44928</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>46125</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46127</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>45414</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>44713</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>46127</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>46199</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>46133</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45385</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>46133</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49311,7 +49311,7 @@
         <v>45392</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>46134</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
         <v>46134</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>46134</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>44889</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45705</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>45111</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45131</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49895,7 +49895,7 @@
         <v>44756</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45063</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>44874</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50119,7 +50119,7 @@
         <v>46078</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50192,7 +50192,7 @@
         <v>45980</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50270,7 +50270,7 @@
         <v>45478</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>46139</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45119</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45644</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>45551</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>44677</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>45931</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45198</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>45301</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>45301</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51005,7 +51005,7 @@
         <v>45512</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>46205</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>44742</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45359</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>44713</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45096</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>45590</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>44798</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>44593</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45098</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>45392</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>44746</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45056</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45118</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>45056</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>45544</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>44827</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>45016</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>44825</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>46272</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>46273</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45095</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>46274</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45244</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>46275</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45211</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45367</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>46279</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45072</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45244</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>46279</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>44999</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45188</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>46238</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>45342</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53570,7 +53570,7 @@
         <v>44910</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45156</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53716,7 +53716,7 @@
         <v>46238</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>44566</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53867,7 +53867,7 @@
         <v>45373</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>45210</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54013,7 +54013,7 @@
         <v>44909</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54086,7 +54086,7 @@
         <v>44909</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54159,7 +54159,7 @@
         <v>45668</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>46282</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>46283</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>45156</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>44866</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54524,7 +54524,7 @@
         <v>44755</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>44594</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>44992</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45373</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45085</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>46175</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45475</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>45205</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>46286</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>46241</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>45401</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45744</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45239</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>45089</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>45079</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45429</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>46246</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55770,7 +55770,7 @@
         <v>45762</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55843,7 +55843,7 @@
         <v>44785</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55916,7 +55916,7 @@
         <v>45113</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55989,7 +55989,7 @@
         <v>44880</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>46246</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56135,7 +56135,7 @@
         <v>44488</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45089</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45208</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>46289</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56427,7 +56427,7 @@
         <v>45534</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56500,7 +56500,7 @@
         <v>45342</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>46134</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         <v>45484</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>44594</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56792,7 +56792,7 @@
         <v>45706</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56865,7 +56865,7 @@
         <v>46250</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56938,7 +56938,7 @@
         <v>46248</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57011,7 +57011,7 @@
         <v>45756</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57084,7 +57084,7 @@
         <v>44700</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>44622</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45240</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57303,7 +57303,7 @@
         <v>45938</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57376,7 +57376,7 @@
         <v>45792</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57454,7 +57454,7 @@
         <v>44865</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>45761</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57605,7 +57605,7 @@
         <v>44749</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>44973</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>45175</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45308</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57897,7 +57897,7 @@
         <v>45149</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>45210</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58043,7 +58043,7 @@
         <v>44881</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58116,7 +58116,7 @@
         <v>46295</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45175</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58262,7 +58262,7 @@
         <v>45371</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>44743</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>44594</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58481,7 +58481,7 @@
         <v>45320</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58554,7 +58554,7 @@
         <v>46112</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45741</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45681</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58778,7 +58778,7 @@
         <v>46255</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>44882</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58929,7 +58929,7 @@
         <v>46253</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59007,7 +59007,7 @@
         <v>46246</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59080,7 +59080,7 @@
         <v>45940</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59153,7 +59153,7 @@
         <v>46252</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59226,7 +59226,7 @@
         <v>46254</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59304,7 +59304,7 @@
         <v>46297</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59377,7 +59377,7 @@
         <v>46029</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59450,7 +59450,7 @@
         <v>46253</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59528,7 +59528,7 @@
         <v>45679</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59601,7 +59601,7 @@
         <v>46300</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59674,7 +59674,7 @@
         <v>45586</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59747,7 +59747,7 @@
         <v>46255</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59820,7 +59820,7 @@
         <v>46300</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59893,7 +59893,7 @@
         <v>46300</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>44606</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60044,7 +60044,7 @@
         <v>46300</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60117,7 +60117,7 @@
         <v>45545</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60190,7 +60190,7 @@
         <v>45449</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60263,7 +60263,7 @@
         <v>46300</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>46300</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>45070</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>45601</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45476</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60638,7 +60638,7 @@
         <v>45489</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60711,7 +60711,7 @@
         <v>46198</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60784,7 +60784,7 @@
         <v>46301</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60857,7 +60857,7 @@
         <v>45587</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60930,7 +60930,7 @@
         <v>46190</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>46300</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61076,7 +61076,7 @@
         <v>45785</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>45230</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61222,7 +61222,7 @@
         <v>46300</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61295,7 +61295,7 @@
         <v>45489</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61368,7 +61368,7 @@
         <v>45625</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61441,7 +61441,7 @@
         <v>45706</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61514,7 +61514,7 @@
         <v>45786</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61587,7 +61587,7 @@
         <v>45673</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61660,7 +61660,7 @@
         <v>45572</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61733,7 +61733,7 @@
         <v>45665</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61806,7 +61806,7 @@
         <v>45534</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61879,7 +61879,7 @@
         <v>45357</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61952,7 +61952,7 @@
         <v>45301</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62025,7 +62025,7 @@
         <v>45401</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62098,7 +62098,7 @@
         <v>46295</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62171,7 +62171,7 @@
         <v>45367</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62244,7 +62244,7 @@
         <v>46301</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62317,7 +62317,7 @@
         <v>45246</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>45370</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62463,7 +62463,7 @@
         <v>46295</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62536,7 +62536,7 @@
         <v>46301</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>46303</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62682,7 +62682,7 @@
         <v>46302</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62755,7 +62755,7 @@
         <v>46261</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>45701</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62901,7 +62901,7 @@
         <v>45761</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62974,7 +62974,7 @@
         <v>46034</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63047,7 +63047,7 @@
         <v>44697</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63120,7 +63120,7 @@
         <v>46181</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63198,7 +63198,7 @@
         <v>46307</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63271,7 +63271,7 @@
         <v>45525</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>45812</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63417,7 +63417,7 @@
         <v>45818</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63490,7 +63490,7 @@
         <v>45821</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>45825</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63636,7 +63636,7 @@
         <v>45824</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63714,7 +63714,7 @@
         <v>46269</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>46269</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63860,7 +63860,7 @@
         <v>45824</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63933,7 +63933,7 @@
         <v>45833</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45834</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64079,7 +64079,7 @@
         <v>45834</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64152,7 +64152,7 @@
         <v>45834</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64225,7 +64225,7 @@
         <v>45834</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64298,7 +64298,7 @@
         <v>45837</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64371,7 +64371,7 @@
         <v>45837</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64444,7 +64444,7 @@
         <v>45616</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64517,7 +64517,7 @@
         <v>45616</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64590,7 +64590,7 @@
         <v>45817</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>45846</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64736,7 +64736,7 @@
         <v>45846</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64809,7 +64809,7 @@
         <v>45852</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64882,7 +64882,7 @@
         <v>45856</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64960,7 +64960,7 @@
         <v>45856</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65038,7 +65038,7 @@
         <v>45818</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65111,7 +65111,7 @@
         <v>45616</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65184,7 +65184,7 @@
         <v>45881</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65262,7 +65262,7 @@
         <v>45880</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65335,7 +65335,7 @@
         <v>45880</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65408,7 +65408,7 @@
         <v>45882</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65481,7 +65481,7 @@
         <v>45882</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65554,7 +65554,7 @@
         <v>45883</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65627,7 +65627,7 @@
         <v>45883</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65700,7 +65700,7 @@
         <v>44665</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65773,7 +65773,7 @@
         <v>44973</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65846,7 +65846,7 @@
         <v>45422</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65919,7 +65919,7 @@
         <v>45649</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65992,7 +65992,7 @@
         <v>45457</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66065,7 +66065,7 @@
         <v>45088</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66138,7 +66138,7 @@
         <v>45469</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66211,7 +66211,7 @@
         <v>45000</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66284,7 +66284,7 @@
         <v>45224</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66357,7 +66357,7 @@
         <v>45572</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66430,7 +66430,7 @@
         <v>45056</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66503,7 +66503,7 @@
         <v>44592</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66576,7 +66576,7 @@
         <v>45558</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66649,7 +66649,7 @@
         <v>44587</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66722,7 +66722,7 @@
         <v>44806</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66795,7 +66795,7 @@
         <v>45649</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66868,7 +66868,7 @@
         <v>45056</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66941,7 +66941,7 @@
         <v>45649</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67014,7 +67014,7 @@
         <v>44594</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67087,7 +67087,7 @@
         <v>44693</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67160,7 +67160,7 @@
         <v>45357</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67233,7 +67233,7 @@
         <v>45088</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67306,7 +67306,7 @@
         <v>45335</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67379,7 +67379,7 @@
         <v>45231</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67452,7 +67452,7 @@
         <v>44587</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67525,7 +67525,7 @@
         <v>45572</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67598,7 +67598,7 @@
         <v>45056</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67671,7 +67671,7 @@
         <v>45750</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67744,7 +67744,7 @@
         <v>45847</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67817,7 +67817,7 @@
         <v>45923</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67890,7 +67890,7 @@
         <v>45919</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67963,7 +67963,7 @@
         <v>45926</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>45982</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68109,7 +68109,7 @@
         <v>45982</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68182,7 +68182,7 @@
         <v>46030</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68255,7 +68255,7 @@
         <v>46244</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68328,7 +68328,7 @@
         <v>46295</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68401,7 +68401,7 @@
         <v>46308</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45649</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>46153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>45006</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>43929</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>45099</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46153</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>45568</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>45889</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45730</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44606</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44839</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44504</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45561</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>46153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>46153</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>44867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45643</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>46164</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46174</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>45999</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>46247</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>46153</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>45093</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>45189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>44592</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>44628</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45056</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>45652</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>46126</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>45316</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>45352</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>45042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>45695</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45888</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>44656</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>46058</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>44748</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44853</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>44593</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45888</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45174</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>45604</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44917</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>45222</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>45149</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44980</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>45649</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>46009</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>45818</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45850</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45075</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>45110</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>46141</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>44785</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45093</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>45154</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>44869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>45188</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>45446</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>45447</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>45104</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44595</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>44607</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>44853</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>45335</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44860</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45813</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>46308</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>44612</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44602</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>45096</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>45898</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>45215</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>44798</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45069</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45111</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>46169</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44966</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44951</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>46183</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>46190</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>44882</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45279</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>46002</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>46002</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>45541</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44909</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45547</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45701</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>46153</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>46057</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>46254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>46300</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>46094</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45616</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>46302</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>46109</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>45940</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45545</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>44908</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>46230</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>45758</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>46078</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>45449</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>46141</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>45581</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>46153</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>46153</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>46153</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45155</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>45594</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>45118</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>44648</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>45307</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>45730</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>44917</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>44603</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>44590</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>44830</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>45572</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>46034</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>46293</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44630</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>44889</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>44691</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>44861</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>44581</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>44844</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>44816</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>44571</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44645</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44565</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>44831</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>44783</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>44566</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>44684</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>44806</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>44493</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>44624</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>44587</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44776</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>44870</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>44771</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>44657</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>44612</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>44617</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44551</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44508</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44851</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>44629</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>44494</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44881</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44796</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>44551</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44593</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44785</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44650</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44839</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>44805</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>44593</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44526</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>44578</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44634</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44634</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>44727</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>44928</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>44594</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44933</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>44551</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45882</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>44870</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44977</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>45169</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44587</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44936</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>44609</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45888</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>44881</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45628</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45188</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45091</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45849</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45253</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45244</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45190</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45166</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45216</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45341</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45072</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45043</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45054</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45685</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45371</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45894</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45894</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>44914</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>45791</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>44497</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>44949</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45512</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>44505</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45510</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45883</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
         <v>45883</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>45260</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>45698</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45603</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>45188</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>44909</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45385</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45056</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>44866</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45798</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>44866</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45852</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>44755</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>44867</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45606</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45075</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45603</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45253</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45603</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45075</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>44982</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45908</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45849</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45342</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>44827</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45840</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>44900</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45213</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44904</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>44909</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45091</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44494</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45917</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45063</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>44798</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>44853</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>45470</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>46168</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>45021</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45079</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45923</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45668</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>45926</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>45336</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>45670</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>44713</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>44908</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>44974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>45079</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45208</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45525</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>46175</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45590</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45078</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>45175</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45938</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>44973</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>45078</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>45093</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>46169</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45488</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45050</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45401</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45149</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>46177</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>45075</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>44890</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45679</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>45103</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>45103</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>45376</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>45440</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44868</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>44880</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45149</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>45469</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>45478</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45945</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45359</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>45946</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>45606</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>45946</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>44586</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45093</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>46178</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>46178</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>46184</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>45162</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>46184</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44839</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44865</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>44909</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>45085</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45958</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45958</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>46182</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45308</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45958</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45958</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45649</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45649</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>45240</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>44785</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45011</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45210</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45110</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>45591</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>45635</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28604,7 +28604,7 @@
         <v>45028</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>44811</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44867</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45429</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>46190</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44594</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45331</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45022</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>44778</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>46197</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45056</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45561</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45205</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>46197</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>46197</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>45103</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>45975</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>45240</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>46199</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>44903</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>45477</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45980</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>45980</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>45980</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>45407</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>44882</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>45069</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>46205</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>45163</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>45373</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>45369</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45986</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45985</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>45356</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>45986</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
         <v>45321</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>44973</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44973</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31413,7 +31413,7 @@
         <v>45013</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45560</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>45987</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>45096</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45679</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45714</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>45649</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45649</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>45217</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>45762</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45999</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>44999</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45666</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>46000</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>45181</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45070</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>44606</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45601</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45449</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>45545</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45476</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45489</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>45587</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45665</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45706</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>46279</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>45572</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45230</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45370</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45246</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45098</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45357</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45367</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45233</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45673</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>44957</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>44957</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>45301</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45625</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>46279</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>45489</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>46282</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>45785</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>46238</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>45786</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>46000</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45401</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>45534</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>46238</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>46029</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>46283</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>46175</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>46241</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45701</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45744</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>46286</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>45761</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>44697</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>46051</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>45525</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>46134</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>46246</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>46246</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45938</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>46289</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44594</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36251,7 +36251,7 @@
         <v>45812</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>46250</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>46248</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>46064</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>46064</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36616,7 +36616,7 @@
         <v>46069</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
         <v>46067</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>46069</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>45818</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>46072</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>46072</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>45342</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45824</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>45821</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37278,7 +37278,7 @@
         <v>45824</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37351,7 +37351,7 @@
         <v>46253</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>45825</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>46295</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37575,7 +37575,7 @@
         <v>46078</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>46083</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>46083</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>46253</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37872,7 +37872,7 @@
         <v>46254</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>45834</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>46087</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>45834</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44528</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>45834</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>45833</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>46086</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>45834</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>46300</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>46246</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>46255</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>46112</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>46029</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>46255</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>46300</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45837</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>46300</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45837</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>46092</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>46092</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>46300</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>46300</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>46300</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>46297</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>46300</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>46300</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45616</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>45846</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>45817</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45846</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45940</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>46252</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40306,7 +40306,7 @@
         <v>46198</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40379,7 +40379,7 @@
         <v>45616</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>46302</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>46104</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>46106</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>46301</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>45852</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>46106</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45341</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>45856</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>45856</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45475</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>46113</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>46190</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>46112</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45475</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>46301</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>46301</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>46112</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>46112</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45818</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>45616</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>46303</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>46261</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>46122</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>46125</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45729</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>46127</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>46127</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45880</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>46307</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44915</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45880</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45881</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>45882</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         <v>46181</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>44972</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>46133</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45791</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45737</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>46134</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>46134</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>46134</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45089</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>45253</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>46034</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>45551</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>46133</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>44914</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>45478</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45547</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>45544</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44132,7 +44132,7 @@
         <v>45966</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45363</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44278,7 +44278,7 @@
         <v>45914</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45930</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>45820</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45841</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45966</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         <v>45705</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45951</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>45478</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45577</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45980</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45023,7 +45023,7 @@
         <v>45931</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45392</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>44904</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>45859</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45975</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>45442</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>45644</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45551</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45931</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45862</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>44959</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45713</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45887</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>45327</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45664</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>46269</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>46052</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>44928</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>46269</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>44544</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>44959</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45077</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>44692</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45946</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46785,7 +46785,7 @@
         <v>45561</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45561</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>45103</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45408</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>46274</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>44992</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>46272</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45534</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>45572</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45098</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>46139</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>44873</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45832</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45145</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47817,7 +47817,7 @@
         <v>45145</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47890,7 +47890,7 @@
         <v>44593</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>46273</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48036,7 +48036,7 @@
         <v>46058</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>45335</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>45222</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>46295</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
         <v>44973</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45385</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>44910</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>46141</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>46141</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45372</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45037</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45392</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>44939</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>45223</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45230</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49141,7 +49141,7 @@
         <v>45367</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>46275</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>46141</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44733</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>46295</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>44867</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49589,7 +49589,7 @@
         <v>44970</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45191</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49740,7 +49740,7 @@
         <v>46153</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45095</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>45695</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         <v>46153</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>44713</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50115,7 +50115,7 @@
         <v>45415</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45071</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45586</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45439</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
         <v>45740</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50480,7 +50480,7 @@
         <v>44825</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45070</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45367</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>45411</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>46155</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>45894</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>46160</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>44713</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>45121</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>45121</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51210,7 +51210,7 @@
         <v>44746</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>46057</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51356,7 +51356,7 @@
         <v>44798</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51429,7 +51429,7 @@
         <v>45307</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51502,7 +51502,7 @@
         <v>45359</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51575,7 +51575,7 @@
         <v>45089</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45629</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>44931</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45106</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45057</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>45057</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>44819</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>45681</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45210</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45475</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>44999</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>45706</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45119</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52539,7 +52539,7 @@
         <v>45484</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52612,7 +52612,7 @@
         <v>45409</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         <v>45694</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52758,7 +52758,7 @@
         <v>45022</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52831,7 +52831,7 @@
         <v>45111</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52904,7 +52904,7 @@
         <v>45231</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52977,7 +52977,7 @@
         <v>44818</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53050,7 +53050,7 @@
         <v>45369</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45762</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>44945</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53274,7 +53274,7 @@
         <v>44494</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53347,7 +53347,7 @@
         <v>45733</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>44991</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53493,7 +53493,7 @@
         <v>45554</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>44816</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>44881</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>44844</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53790,7 +53790,7 @@
         <v>45509</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53863,7 +53863,7 @@
         <v>45189</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45728</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>44700</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54092,7 +54092,7 @@
         <v>45072</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54165,7 +54165,7 @@
         <v>44889</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45135</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54311,7 +54311,7 @@
         <v>45055</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45111</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54457,7 +54457,7 @@
         <v>45761</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54535,7 +54535,7 @@
         <v>45426</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45763</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>44874</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54754,7 +54754,7 @@
         <v>45013</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>45090</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54900,7 +54900,7 @@
         <v>44882</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54973,7 +54973,7 @@
         <v>45210</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55046,7 +55046,7 @@
         <v>45296</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55119,7 +55119,7 @@
         <v>44825</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45342</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45096</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55338,7 +55338,7 @@
         <v>45103</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45575</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55484,7 +55484,7 @@
         <v>45156</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55557,7 +55557,7 @@
         <v>45313</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55630,7 +55630,7 @@
         <v>45761</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55703,7 +55703,7 @@
         <v>45394</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45368</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55854,7 +55854,7 @@
         <v>45369</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55927,7 +55927,7 @@
         <v>45118</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>45121</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>45280</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>45123</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         <v>45117</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>45084</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>45561</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56438,7 +56438,7 @@
         <v>45079</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45107</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56584,7 +56584,7 @@
         <v>44953</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45156</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56730,7 +56730,7 @@
         <v>45429</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56803,7 +56803,7 @@
         <v>44938</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56876,7 +56876,7 @@
         <v>44973</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56949,7 +56949,7 @@
         <v>45744</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57022,7 +57022,7 @@
         <v>45260</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>45616</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57168,7 +57168,7 @@
         <v>45096</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
         <v>45474</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57314,7 +57314,7 @@
         <v>45169</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57387,7 +57387,7 @@
         <v>44580</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57460,7 +57460,7 @@
         <v>45079</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57533,7 +57533,7 @@
         <v>45320</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57606,7 +57606,7 @@
         <v>45113</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57679,7 +57679,7 @@
         <v>45131</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57752,7 +57752,7 @@
         <v>45763</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45315</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57898,7 +57898,7 @@
         <v>45016</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>45561</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58049,7 +58049,7 @@
         <v>44566</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>45092</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58200,7 +58200,7 @@
         <v>45197</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45035</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58346,7 +58346,7 @@
         <v>44832</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45218</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58497,7 +58497,7 @@
         <v>45338</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58570,7 +58570,7 @@
         <v>45560</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58643,7 +58643,7 @@
         <v>44645</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58716,7 +58716,7 @@
         <v>45664</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58789,7 +58789,7 @@
         <v>44677</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58862,7 +58862,7 @@
         <v>45373</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>45063</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>45082</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59086,7 +59086,7 @@
         <v>45191</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>44657</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         <v>44594</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59315,7 +59315,7 @@
         <v>45049</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>44622</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59461,7 +59461,7 @@
         <v>45637</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59534,7 +59534,7 @@
         <v>45072</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59607,7 +59607,7 @@
         <v>45762</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59685,7 +59685,7 @@
         <v>45118</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59758,7 +59758,7 @@
         <v>45392</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59831,7 +59831,7 @@
         <v>45196</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59904,7 +59904,7 @@
         <v>44833</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59977,7 +59977,7 @@
         <v>44690</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60050,7 +60050,7 @@
         <v>44684</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60123,7 +60123,7 @@
         <v>45182</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60196,7 +60196,7 @@
         <v>45175</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60269,7 +60269,7 @@
         <v>45093</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60342,7 +60342,7 @@
         <v>45244</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60415,7 +60415,7 @@
         <v>45741</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60488,7 +60488,7 @@
         <v>45756</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60561,7 +60561,7 @@
         <v>45211</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60634,7 +60634,7 @@
         <v>45187</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60707,7 +60707,7 @@
         <v>45407</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60780,7 +60780,7 @@
         <v>45239</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60853,7 +60853,7 @@
         <v>44742</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60926,7 +60926,7 @@
         <v>44909</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60999,7 +60999,7 @@
         <v>45175</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61072,7 +61072,7 @@
         <v>45198</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61145,7 +61145,7 @@
         <v>45211</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>44749</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61291,7 +61291,7 @@
         <v>44721</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>44743</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45175</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61510,7 +61510,7 @@
         <v>45414</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61583,7 +61583,7 @@
         <v>45756</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61656,7 +61656,7 @@
         <v>44909</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61729,7 +61729,7 @@
         <v>45244</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61802,7 +61802,7 @@
         <v>44841</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61875,7 +61875,7 @@
         <v>45775</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61948,7 +61948,7 @@
         <v>44803</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62021,7 +62021,7 @@
         <v>44693</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62099,7 +62099,7 @@
         <v>45448</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62172,7 +62172,7 @@
         <v>44739</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>44746</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62318,7 +62318,7 @@
         <v>45254</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62391,7 +62391,7 @@
         <v>45330</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>44497</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62537,7 +62537,7 @@
         <v>44974</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62610,7 +62610,7 @@
         <v>45366</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62683,7 +62683,7 @@
         <v>45217</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62756,7 +62756,7 @@
         <v>44917</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62834,7 +62834,7 @@
         <v>44959</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62907,7 +62907,7 @@
         <v>45273</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62980,7 +62980,7 @@
         <v>44819</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63058,7 +63058,7 @@
         <v>45301</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63131,7 +63131,7 @@
         <v>45301</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63204,7 +63204,7 @@
         <v>45763</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63277,7 +63277,7 @@
         <v>45327</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63350,7 +63350,7 @@
         <v>45092</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63428,7 +63428,7 @@
         <v>45346</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63501,7 +63501,7 @@
         <v>45728</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63579,7 +63579,7 @@
         <v>45278</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63652,7 +63652,7 @@
         <v>45090</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63725,7 +63725,7 @@
         <v>45610</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63798,7 +63798,7 @@
         <v>44756</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63876,7 +63876,7 @@
         <v>45091</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>44868</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64022,7 +64022,7 @@
         <v>44621</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64095,7 +64095,7 @@
         <v>45484</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64168,7 +64168,7 @@
         <v>44865</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64241,7 +64241,7 @@
         <v>44985</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64314,7 +64314,7 @@
         <v>45463</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64387,7 +64387,7 @@
         <v>45534</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64460,7 +64460,7 @@
         <v>45394</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64538,7 +64538,7 @@
         <v>45090</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64611,7 +64611,7 @@
         <v>45342</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64684,7 +64684,7 @@
         <v>45400</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64757,7 +64757,7 @@
         <v>45552</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64830,7 +64830,7 @@
         <v>44909</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64903,7 +64903,7 @@
         <v>44973</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64976,7 +64976,7 @@
         <v>44904</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65049,7 +65049,7 @@
         <v>45174</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65122,7 +65122,7 @@
         <v>45335</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>44992</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65273,7 +65273,7 @@
         <v>44579</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65346,7 +65346,7 @@
         <v>44665</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65419,7 +65419,7 @@
         <v>44592</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65492,7 +65492,7 @@
         <v>44587</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65565,7 +65565,7 @@
         <v>44594</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65638,7 +65638,7 @@
         <v>44693</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65711,7 +65711,7 @@
         <v>44587</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65784,7 +65784,7 @@
         <v>44973</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65857,7 +65857,7 @@
         <v>45422</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65930,7 +65930,7 @@
         <v>45649</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66003,7 +66003,7 @@
         <v>45457</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66076,7 +66076,7 @@
         <v>45088</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>45469</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66222,7 +66222,7 @@
         <v>45000</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66295,7 +66295,7 @@
         <v>45224</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66368,7 +66368,7 @@
         <v>45572</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66441,7 +66441,7 @@
         <v>45056</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66514,7 +66514,7 @@
         <v>45558</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66587,7 +66587,7 @@
         <v>44806</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66660,7 +66660,7 @@
         <v>45649</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66733,7 +66733,7 @@
         <v>45056</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66806,7 +66806,7 @@
         <v>45649</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66879,7 +66879,7 @@
         <v>45357</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66952,7 +66952,7 @@
         <v>45088</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67025,7 +67025,7 @@
         <v>45335</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67098,7 +67098,7 @@
         <v>45231</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67171,7 +67171,7 @@
         <v>45572</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67244,7 +67244,7 @@
         <v>45056</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67317,7 +67317,7 @@
         <v>45750</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67390,7 +67390,7 @@
         <v>45847</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67463,7 +67463,7 @@
         <v>45923</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67536,7 +67536,7 @@
         <v>45919</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67609,7 +67609,7 @@
         <v>45926</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67682,7 +67682,7 @@
         <v>45982</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67755,7 +67755,7 @@
         <v>45982</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67828,7 +67828,7 @@
         <v>46030</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67901,7 +67901,7 @@
         <v>46244</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67974,7 +67974,7 @@
         <v>46295</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68047,7 +68047,7 @@
         <v>46308</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>

--- a/Översikt NYBRO.xlsx
+++ b/Översikt NYBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45649</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>46153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>45006</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>43929</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>45099</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46153</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>45568</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>45889</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45730</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44606</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44839</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44504</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45561</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>46153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>46153</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>44867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45643</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44587</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>46164</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46174</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>45999</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>46247</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>46153</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>45093</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>45189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>44592</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>44628</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45056</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>45652</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>46126</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>45316</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>45352</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>45042</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>45695</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45888</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>44656</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>46058</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>44748</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44853</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>44593</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45888</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45174</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>45604</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44917</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>45222</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>45149</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44980</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>45649</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>46009</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>45818</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45850</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45075</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>45110</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>46141</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>44785</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45093</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>45154</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>44869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>45188</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>45446</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>45447</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>45104</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44595</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>44607</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>44853</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>45335</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44860</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45813</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>46308</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>44612</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44602</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>45096</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>45898</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>45215</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>44798</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45069</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45111</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>46169</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44966</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44951</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>46183</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>46190</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>44882</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45279</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>46002</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>46002</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>45541</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44909</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45547</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45701</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>46153</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>46057</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>46254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>46300</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>46094</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45616</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>46302</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>46109</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>45940</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45545</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>44908</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>46230</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>45758</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>46078</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>45449</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>46141</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>45581</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>46153</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>46153</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>46153</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45155</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>45594</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>45118</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>44648</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>45307</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>45730</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>44917</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>44603</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>44590</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>44830</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>45572</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>46034</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>46293</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44630</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>44889</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>44691</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>44861</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>44581</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>44844</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>44816</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>44571</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44645</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44565</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>44831</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>44783</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>44566</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>44684</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>44806</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>44493</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>44624</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>44587</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44776</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>44870</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>44771</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>44657</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>44612</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>44617</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44551</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44508</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44851</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>44629</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>44494</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44881</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44796</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>44551</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44593</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44785</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44650</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44839</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>44805</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>44593</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44526</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>44578</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44634</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44634</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>44727</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>44928</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>44594</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44933</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>44551</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45882</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>44870</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44977</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>45169</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44587</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44936</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>44609</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45888</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>44881</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45628</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45188</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45091</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45849</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45253</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45244</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45190</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45166</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45216</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45341</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45072</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45043</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45054</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45685</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45371</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45894</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45894</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>44914</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>45791</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>44497</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>44949</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45512</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>44505</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45510</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45883</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
         <v>45883</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>45260</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>45698</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45603</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>45188</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>44909</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45385</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45056</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>44866</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45798</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>44866</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45852</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>44755</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>44867</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45606</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45075</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45603</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45253</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45603</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45075</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>44982</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45908</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45849</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45342</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>44827</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45840</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>44900</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45213</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44904</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>44909</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45091</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44494</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45917</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45063</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>44798</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>44853</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>45470</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>46168</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>45021</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45079</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45923</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45668</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>45926</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>45336</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>45670</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>44713</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>44908</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>44974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>45079</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45208</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45525</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>46175</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45590</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45078</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>45175</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45938</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>44973</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>45078</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>45093</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>46169</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45488</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45050</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45401</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45149</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>46177</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>45075</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>44890</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45679</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>45103</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>45103</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>45376</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>45440</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44868</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>44880</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45149</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>45469</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>45478</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45945</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45359</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>45946</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>45606</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>45946</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>44586</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45093</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>46178</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>46178</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>46184</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>45162</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>46184</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44839</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44865</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>44909</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>45085</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45958</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45958</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>46182</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45308</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45958</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45958</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45649</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45649</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>45240</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>44785</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45011</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45210</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45110</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>45591</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>45635</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28604,7 +28604,7 @@
         <v>45028</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>44811</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44867</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45429</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>46190</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44594</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45331</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45022</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>44778</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>46197</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45056</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45561</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45205</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>46197</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>46197</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>45103</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>45975</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>45240</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>46199</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>44903</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>45477</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45980</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>45980</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>45980</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>45407</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>44882</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>45069</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>46205</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>45163</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>45373</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>45369</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45986</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45985</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>45356</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>45986</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
         <v>45321</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>44973</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44973</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31413,7 +31413,7 @@
         <v>45013</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45560</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>45987</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>45096</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45679</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45714</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>45649</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45649</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>45217</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>45762</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45999</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>44999</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45666</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>46000</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>45181</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45070</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>44606</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45601</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45449</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>45545</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45476</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45489</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>45587</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45665</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45706</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>46279</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>45572</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45230</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45370</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45246</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45098</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45357</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45367</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45233</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45673</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>44957</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>44957</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>45301</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45625</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>46279</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>45489</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>46282</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>45785</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>46238</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>45786</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>46000</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45401</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>45534</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>46238</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>46029</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>46283</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>46175</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>46241</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45701</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45744</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>46286</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>45761</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>44697</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>46051</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>45525</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>46134</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>46246</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>46246</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45938</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>46289</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44594</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36251,7 +36251,7 @@
         <v>45812</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>46250</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>46248</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>46064</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>46064</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36616,7 +36616,7 @@
         <v>46069</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
         <v>46067</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>46069</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>45818</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>46072</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>46072</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>45342</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45824</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>45821</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37278,7 +37278,7 @@
         <v>45824</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37351,7 +37351,7 @@
         <v>46253</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>45825</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>46295</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37575,7 +37575,7 @@
         <v>46078</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>46083</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>46083</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>46253</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37872,7 +37872,7 @@
         <v>46254</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>45834</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>46087</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>45834</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44528</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>45834</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>45833</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>46086</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>45834</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>46300</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>46246</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>46255</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>46112</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>46029</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>46255</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>46300</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45837</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>46300</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45837</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>46092</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>46092</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>46300</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>46300</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>46300</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>46297</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>46300</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>46300</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45616</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>45846</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>45817</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45846</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45940</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>46252</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40306,7 +40306,7 @@
         <v>46198</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40379,7 +40379,7 @@
         <v>45616</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>46302</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>46104</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>46106</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>46301</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>45852</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>46106</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45341</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>45856</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>45856</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45475</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>46113</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>46190</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>46112</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45475</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>46301</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>46301</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>46112</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>46112</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45818</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>45616</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>46303</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>46261</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>46122</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>46125</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45729</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>46127</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>46127</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45880</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>46307</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44915</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45880</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45881</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>45882</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         <v>46181</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>44972</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>46133</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45791</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45737</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>46134</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>46134</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>46134</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45089</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>45253</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>46034</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>45551</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>46133</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>44914</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>45478</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45547</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>45544</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44132,7 +44132,7 @@
         <v>45966</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45363</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44278,7 +44278,7 @@
         <v>45914</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45930</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>45820</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45841</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45966</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         <v>45705</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45951</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>45478</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45577</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45980</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45023,7 +45023,7 @@
         <v>45931</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45101,7 +45101,7 @@
         <v>45392</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>44904</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>45859</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45975</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>45442</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>45644</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45551</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45931</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45862</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>44959</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45713</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45887</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>45327</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45664</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>46269</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>46052</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>44928</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>46269</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>44544</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>44959</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45077</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>44692</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45946</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46785,7 +46785,7 @@
         <v>45561</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45561</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>45103</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45408</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>46274</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>44992</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>46272</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45534</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>45572</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45098</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>46139</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>44873</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45832</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45145</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47817,7 +47817,7 @@
         <v>45145</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47890,7 +47890,7 @@
         <v>44593</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>46273</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48036,7 +48036,7 @@
         <v>46058</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>45335</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>45222</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>46295</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
         <v>44973</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45385</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>44910</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>46141</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>46141</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45372</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45037</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45392</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>44939</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>45223</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45230</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49141,7 +49141,7 @@
         <v>45367</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>46275</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>46141</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44733</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>46295</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>44867</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49589,7 +49589,7 @@
         <v>44970</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45191</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49740,7 +49740,7 @@
         <v>46153</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45095</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>45695</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         <v>46153</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>44713</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50115,7 +50115,7 @@
         <v>45415</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45071</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45586</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45439</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
         <v>45740</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50480,7 +50480,7 @@
         <v>44825</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45070</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45367</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>45411</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>46155</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>45894</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>46160</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>44713</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>45121</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>45121</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51210,7 +51210,7 @@
         <v>44746</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>46057</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51356,7 +51356,7 @@
         <v>44798</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51429,7 +51429,7 @@
         <v>45307</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51502,7 +51502,7 @@
         <v>45359</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51575,7 +51575,7 @@
         <v>45089</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45629</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>44931</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45106</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45057</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>45057</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>44819</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>45681</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45210</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45475</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>44999</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>45706</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45119</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52539,7 +52539,7 @@
         <v>45484</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52612,7 +52612,7 @@
         <v>45409</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52685,7 +52685,7 @@
         <v>45694</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52758,7 +52758,7 @@
         <v>45022</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52831,7 +52831,7 @@
         <v>45111</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52904,7 +52904,7 @@
         <v>45231</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52977,7 +52977,7 @@
         <v>44818</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53050,7 +53050,7 @@
         <v>45369</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45762</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>44945</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53274,7 +53274,7 @@
         <v>44494</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53347,7 +53347,7 @@
         <v>45733</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>44991</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53493,7 +53493,7 @@
         <v>45554</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>44816</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>44881</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>44844</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53790,7 +53790,7 @@
         <v>45509</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53863,7 +53863,7 @@
         <v>45189</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45728</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>44700</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54092,7 +54092,7 @@
         <v>45072</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54165,7 +54165,7 @@
         <v>44889</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45135</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54311,7 +54311,7 @@
         <v>45055</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45111</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54457,7 +54457,7 @@
         <v>45761</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54535,7 +54535,7 @@
         <v>45426</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45763</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>44874</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54754,7 +54754,7 @@
         <v>45013</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>45090</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54900,7 +54900,7 @@
         <v>44882</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54973,7 +54973,7 @@
         <v>45210</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55046,7 +55046,7 @@
         <v>45296</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55119,7 +55119,7 @@
         <v>44825</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45342</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45096</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55338,7 +55338,7 @@
         <v>45103</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45575</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55484,7 +55484,7 @@
         <v>45156</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55557,7 +55557,7 @@
         <v>45313</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55630,7 +55630,7 @@
         <v>45761</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55703,7 +55703,7 @@
         <v>45394</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45368</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55854,7 +55854,7 @@
         <v>45369</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55927,7 +55927,7 @@
         <v>45118</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>45121</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>45280</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>45123</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         <v>45117</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>45084</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>45561</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56438,7 +56438,7 @@
         <v>45079</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>45107</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56584,7 +56584,7 @@
         <v>44953</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45156</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56730,7 +56730,7 @@
         <v>45429</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56803,7 +56803,7 @@
         <v>44938</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56876,7 +56876,7 @@
         <v>44973</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56949,7 +56949,7 @@
         <v>45744</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57022,7 +57022,7 @@
         <v>45260</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>45616</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57168,7 +57168,7 @@
         <v>45096</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
         <v>45474</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57314,7 +57314,7 @@
         <v>45169</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57387,7 +57387,7 @@
         <v>44580</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57460,7 +57460,7 @@
         <v>45079</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57533,7 +57533,7 @@
         <v>45320</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57606,7 +57606,7 @@
         <v>45113</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57679,7 +57679,7 @@
         <v>45131</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57752,7 +57752,7 @@
         <v>45763</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45315</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57898,7 +57898,7 @@
         <v>45016</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>45561</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58049,7 +58049,7 @@
         <v>44566</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>45092</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58200,7 +58200,7 @@
         <v>45197</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45035</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58346,7 +58346,7 @@
         <v>44832</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45218</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58497,7 +58497,7 @@
         <v>45338</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58570,7 +58570,7 @@
         <v>45560</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58643,7 +58643,7 @@
         <v>44645</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58716,7 +58716,7 @@
         <v>45664</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58789,7 +58789,7 @@
         <v>44677</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58862,7 +58862,7 @@
         <v>45373</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>45063</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>45082</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59086,7 +59086,7 @@
         <v>45191</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>44657</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         <v>44594</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59315,7 +59315,7 @@
         <v>45049</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>44622</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59461,7 +59461,7 @@
         <v>45637</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59534,7 +59534,7 @@
         <v>45072</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59607,7 +59607,7 @@
         <v>45762</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59685,7 +59685,7 @@
         <v>45118</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59758,7 +59758,7 @@
         <v>45392</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59831,7 +59831,7 @@
         <v>45196</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59904,7 +59904,7 @@
         <v>44833</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59977,7 +59977,7 @@
         <v>44690</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60050,7 +60050,7 @@
         <v>44684</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60123,7 +60123,7 @@
         <v>45182</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60196,7 +60196,7 @@
         <v>45175</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60269,7 +60269,7 @@
         <v>45093</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60342,7 +60342,7 @@
         <v>45244</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60415,7 +60415,7 @@
         <v>45741</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60488,7 +60488,7 @@
         <v>45756</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60561,7 +60561,7 @@
         <v>45211</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60634,7 +60634,7 @@
         <v>45187</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60707,7 +60707,7 @@
         <v>45407</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60780,7 +60780,7 @@
         <v>45239</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60853,7 +60853,7 @@
         <v>44742</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60926,7 +60926,7 @@
         <v>44909</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60999,7 +60999,7 @@
         <v>45175</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61072,7 +61072,7 @@
         <v>45198</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61145,7 +61145,7 @@
         <v>45211</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>44749</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61291,7 +61291,7 @@
         <v>44721</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>44743</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45175</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61510,7 +61510,7 @@
         <v>45414</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61583,7 +61583,7 @@
         <v>45756</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61656,7 +61656,7 @@
         <v>44909</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61729,7 +61729,7 @@
         <v>45244</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61802,7 +61802,7 @@
         <v>44841</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61875,7 +61875,7 @@
         <v>45775</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61948,7 +61948,7 @@
         <v>44803</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62021,7 +62021,7 @@
         <v>44693</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62099,7 +62099,7 @@
         <v>45448</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62172,7 +62172,7 @@
         <v>44739</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>44746</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62318,7 +62318,7 @@
         <v>45254</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62391,7 +62391,7 @@
         <v>45330</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>44497</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62537,7 +62537,7 @@
         <v>44974</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62610,7 +62610,7 @@
         <v>45366</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62683,7 +62683,7 @@
         <v>45217</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62756,7 +62756,7 @@
         <v>44917</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62834,7 +62834,7 @@
         <v>44959</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62907,7 +62907,7 @@
         <v>45273</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62980,7 +62980,7 @@
         <v>44819</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63058,7 +63058,7 @@
         <v>45301</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63131,7 +63131,7 @@
         <v>45301</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63204,7 +63204,7 @@
         <v>45763</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63277,7 +63277,7 @@
         <v>45327</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63350,7 +63350,7 @@
         <v>45092</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63428,7 +63428,7 @@
         <v>45346</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63501,7 +63501,7 @@
         <v>45728</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63579,7 +63579,7 @@
         <v>45278</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63652,7 +63652,7 @@
         <v>45090</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63725,7 +63725,7 @@
         <v>45610</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63798,7 +63798,7 @@
         <v>44756</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63876,7 +63876,7 @@
         <v>45091</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>44868</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64022,7 +64022,7 @@
         <v>44621</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64095,7 +64095,7 @@
         <v>45484</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64168,7 +64168,7 @@
         <v>44865</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64241,7 +64241,7 @@
         <v>44985</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64314,7 +64314,7 @@
         <v>45463</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64387,7 +64387,7 @@
         <v>45534</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64460,7 +64460,7 @@
         <v>45394</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64538,7 +64538,7 @@
         <v>45090</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64611,7 +64611,7 @@
         <v>45342</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64684,7 +64684,7 @@
         <v>45400</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64757,7 +64757,7 @@
         <v>45552</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64830,7 +64830,7 @@
         <v>44909</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64903,7 +64903,7 @@
         <v>44973</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64976,7 +64976,7 @@
         <v>44904</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65049,7 +65049,7 @@
         <v>45174</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65122,7 +65122,7 @@
         <v>45335</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>44992</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65273,7 +65273,7 @@
         <v>44579</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65346,7 +65346,7 @@
         <v>44665</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65419,7 +65419,7 @@
         <v>44592</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65492,7 +65492,7 @@
         <v>44587</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65565,7 +65565,7 @@
         <v>44594</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65638,7 +65638,7 @@
         <v>44693</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65711,7 +65711,7 @@
         <v>44587</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65784,7 +65784,7 @@
         <v>44973</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65857,7 +65857,7 @@
         <v>45422</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65930,7 +65930,7 @@
         <v>45649</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66003,7 +66003,7 @@
         <v>45457</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66076,7 +66076,7 @@
         <v>45088</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>45469</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66222,7 +66222,7 @@
         <v>45000</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66295,7 +66295,7 @@
         <v>45224</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66368,7 +66368,7 @@
         <v>45572</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66441,7 +66441,7 @@
         <v>45056</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66514,7 +66514,7 @@
         <v>45558</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66587,7 +66587,7 @@
         <v>44806</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66660,7 +66660,7 @@
         <v>45649</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66733,7 +66733,7 @@
         <v>45056</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66806,7 +66806,7 @@
         <v>45649</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66879,7 +66879,7 @@
         <v>45357</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66952,7 +66952,7 @@
         <v>45088</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67025,7 +67025,7 @@
         <v>45335</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67098,7 +67098,7 @@
         <v>45231</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67171,7 +67171,7 @@
         <v>45572</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67244,7 +67244,7 @@
         <v>45056</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67317,7 +67317,7 @@
         <v>45750</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67390,7 +67390,7 @@
         <v>45847</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67463,7 +67463,7 @@
         <v>45923</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67536,7 +67536,7 @@
         <v>45919</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67609,7 +67609,7 @@
         <v>45926</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67682,7 +67682,7 @@
         <v>45982</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67755,7 +67755,7 @@
         <v>45982</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67828,7 +67828,7 @@
         <v>46030</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67901,7 +67901,7 @@
         <v>46244</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67974,7 +67974,7 @@
         <v>46295</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68047,7 +68047,7 @@
         <v>46308</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
